--- a/backend/temp_schedule.xlsx
+++ b/backend/temp_schedule.xlsx
@@ -1691,13 +1691,13 @@
         <v>1</v>
       </c>
       <c r="I29" s="18">
-        <v>1999280.8</v>
+        <v>1999280</v>
       </c>
       <c r="J29" s="18">
-        <v>1999280.8</v>
+        <v>0</v>
       </c>
       <c r="K29" s="17">
-        <v>0.55759234</v>
+        <v>0</v>
       </c>
       <c r="L29" s="11"/>
       <c r="M29" s="20">
@@ -1802,10 +1802,10 @@
         <v>300000</v>
       </c>
       <c r="J32" s="18">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="K32" s="17">
-        <v>0.08366897</v>
+        <v>0</v>
       </c>
       <c r="L32" s="11"/>
       <c r="M32" s="20">
@@ -1858,10 +1858,10 @@
         <v>150000</v>
       </c>
       <c r="J33" s="18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K33" s="17">
-        <v>0.04183449</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11"/>
       <c r="M33" s="20">
@@ -1966,10 +1966,10 @@
         <v>25000</v>
       </c>
       <c r="J36" s="18">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="K36" s="17">
-        <v>0.03486207</v>
+        <v>0</v>
       </c>
       <c r="L36" s="11"/>
       <c r="M36" s="20">
@@ -2022,10 +2022,10 @@
         <v>60000</v>
       </c>
       <c r="J37" s="18">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="K37" s="17">
-        <v>0.01673379</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11"/>
       <c r="M37" s="20">
@@ -2078,10 +2078,10 @@
         <v>68000</v>
       </c>
       <c r="J38" s="18">
-        <v>340000</v>
+        <v>0</v>
       </c>
       <c r="K38" s="17">
-        <v>0.09482484</v>
+        <v>0</v>
       </c>
       <c r="L38" s="11"/>
       <c r="M38" s="20">
@@ -2134,10 +2134,10 @@
         <v>35000</v>
       </c>
       <c r="J39" s="18">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="K39" s="17">
-        <v>0.0488069</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11"/>
       <c r="M39" s="20">
@@ -2242,10 +2242,10 @@
         <v>800000</v>
       </c>
       <c r="J42" s="18">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="17">
-        <v>0.22311726</v>
+        <v>0</v>
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="20">
@@ -2350,10 +2350,10 @@
         <v>1500000</v>
       </c>
       <c r="J45" s="18">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="K45" s="17">
-        <v>0.41834486</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11"/>
       <c r="M45" s="20">
@@ -2458,10 +2458,10 @@
         <v>85000</v>
       </c>
       <c r="J48" s="18">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="K48" s="17">
-        <v>0.02370621</v>
+        <v>0</v>
       </c>
       <c r="L48" s="11"/>
       <c r="M48" s="20">
@@ -2498,10 +2498,10 @@
         <v>85000</v>
       </c>
       <c r="J49" s="18">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="K49" s="17">
-        <v>0.02370621</v>
+        <v>0</v>
       </c>
       <c r="L49" s="11"/>
       <c r="M49" s="20">
@@ -2590,10 +2590,10 @@
         <v>5500</v>
       </c>
       <c r="J52" s="18">
-        <v>1140625.2</v>
+        <v>0</v>
       </c>
       <c r="K52" s="17">
-        <v>0.31811646</v>
+        <v>0</v>
       </c>
       <c r="L52" s="11"/>
       <c r="M52" s="20">
@@ -2632,10 +2632,10 @@
         <v>255550</v>
       </c>
       <c r="J53" s="18">
-        <v>52997594.52</v>
+        <v>0</v>
       </c>
       <c r="K53" s="17">
-        <v>14.78084761</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11"/>
       <c r="M53" s="17"/>
@@ -2678,10 +2678,10 @@
         <v>26853</v>
       </c>
       <c r="J54" s="18">
-        <v>2684225.88</v>
+        <v>0</v>
       </c>
       <c r="K54" s="17">
-        <v>0.74862141</v>
+        <v>0</v>
       </c>
       <c r="L54" s="11"/>
       <c r="M54" s="17"/>
@@ -2724,10 +2724,10 @@
         <v>61335</v>
       </c>
       <c r="J55" s="18">
-        <v>9363401.1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="17">
-        <v>2.6114205</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11"/>
       <c r="M55" s="17"/>
@@ -2770,10 +2770,10 @@
         <v>449902</v>
       </c>
       <c r="J56" s="18">
-        <v>5398824</v>
+        <v>0</v>
       </c>
       <c r="K56" s="17">
-        <v>1.50571352</v>
+        <v>0</v>
       </c>
       <c r="L56" s="11"/>
       <c r="M56" s="20">
@@ -2812,10 +2812,10 @@
         <v>668187</v>
       </c>
       <c r="J57" s="18">
-        <v>8018244</v>
+        <v>0</v>
       </c>
       <c r="K57" s="17">
-        <v>2.23626079</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11"/>
       <c r="M57" s="17"/>
@@ -2858,10 +2858,10 @@
         <v>63699</v>
       </c>
       <c r="J58" s="18">
-        <v>191097</v>
+        <v>0</v>
       </c>
       <c r="K58" s="17">
-        <v>0.0532963</v>
+        <v>0</v>
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="17"/>
@@ -2956,10 +2956,10 @@
         <v>5500</v>
       </c>
       <c r="J61" s="18">
-        <v>791076</v>
+        <v>0</v>
       </c>
       <c r="K61" s="17">
-        <v>0.22062839</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11"/>
       <c r="M61" s="20">
@@ -2998,10 +2998,10 @@
         <v>255550</v>
       </c>
       <c r="J62" s="18">
-        <v>36756267.6</v>
+        <v>0</v>
       </c>
       <c r="K62" s="17">
-        <v>10.25119715</v>
+        <v>0</v>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" s="17"/>
@@ -3044,10 +3044,10 @@
         <v>26853</v>
       </c>
       <c r="J63" s="18">
-        <v>1828152.24</v>
+        <v>0</v>
       </c>
       <c r="K63" s="17">
-        <v>0.5098654</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11"/>
       <c r="M63" s="17"/>
@@ -3090,10 +3090,10 @@
         <v>61335</v>
       </c>
       <c r="J64" s="18">
-        <v>6016350.15</v>
+        <v>0</v>
       </c>
       <c r="K64" s="17">
-        <v>1.67793945</v>
+        <v>0</v>
       </c>
       <c r="L64" s="11"/>
       <c r="M64" s="17"/>
@@ -3136,10 +3136,10 @@
         <v>449902</v>
       </c>
       <c r="J65" s="18">
-        <v>3599216</v>
+        <v>0</v>
       </c>
       <c r="K65" s="17">
-        <v>1.00380902</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11"/>
       <c r="M65" s="20">
@@ -3178,10 +3178,10 @@
         <v>668187</v>
       </c>
       <c r="J66" s="18">
-        <v>5345496</v>
+        <v>0</v>
       </c>
       <c r="K66" s="17">
-        <v>1.49084053</v>
+        <v>0</v>
       </c>
       <c r="L66" s="11"/>
       <c r="M66" s="17"/>
@@ -3224,10 +3224,10 @@
         <v>63699</v>
       </c>
       <c r="J67" s="18">
-        <v>127398</v>
+        <v>0</v>
       </c>
       <c r="K67" s="17">
-        <v>0.03553087</v>
+        <v>0</v>
       </c>
       <c r="L67" s="11"/>
       <c r="M67" s="17"/>
@@ -3350,10 +3350,10 @@
         <v>5500</v>
       </c>
       <c r="J71" s="18">
-        <v>27610</v>
+        <v>0</v>
       </c>
       <c r="K71" s="17">
-        <v>0.00770033</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11"/>
       <c r="M71" s="17"/>
@@ -3390,10 +3390,10 @@
         <v>255550</v>
       </c>
       <c r="J72" s="18">
-        <v>1282861</v>
+        <v>0</v>
       </c>
       <c r="K72" s="17">
-        <v>0.35778554</v>
+        <v>0</v>
       </c>
       <c r="L72" s="11"/>
       <c r="M72" s="17"/>
@@ -3432,10 +3432,10 @@
         <v>26853</v>
       </c>
       <c r="J73" s="18">
-        <v>341033.1</v>
+        <v>0</v>
       </c>
       <c r="K73" s="17">
-        <v>0.09511296</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11"/>
       <c r="M73" s="17"/>
@@ -3474,10 +3474,10 @@
         <v>61335</v>
       </c>
       <c r="J74" s="18">
-        <v>122670</v>
+        <v>0</v>
       </c>
       <c r="K74" s="17">
-        <v>0.03421224</v>
+        <v>0</v>
       </c>
       <c r="L74" s="11"/>
       <c r="M74" s="17"/>
@@ -3516,10 +3516,10 @@
         <v>449902</v>
       </c>
       <c r="J75" s="18">
-        <v>899804</v>
+        <v>0</v>
       </c>
       <c r="K75" s="17">
-        <v>0.25095225</v>
+        <v>0</v>
       </c>
       <c r="L75" s="11"/>
       <c r="M75" s="17"/>
@@ -3558,10 +3558,10 @@
         <v>63699</v>
       </c>
       <c r="J76" s="18">
-        <v>127398</v>
+        <v>0</v>
       </c>
       <c r="K76" s="17">
-        <v>0.03553087</v>
+        <v>0</v>
       </c>
       <c r="L76" s="11"/>
       <c r="M76" s="17"/>
@@ -3652,10 +3652,10 @@
         <v>97486</v>
       </c>
       <c r="J79" s="18">
-        <v>1131081.315</v>
+        <v>0</v>
       </c>
       <c r="K79" s="17">
-        <v>0.31545471</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11"/>
       <c r="M79" s="20">
@@ -3692,10 +3692,10 @@
         <v>5500</v>
       </c>
       <c r="J80" s="18">
-        <v>746620.875</v>
+        <v>0</v>
       </c>
       <c r="K80" s="17">
-        <v>0.20823001</v>
+        <v>0</v>
       </c>
       <c r="L80" s="11"/>
       <c r="M80" s="20">
@@ -3732,10 +3732,10 @@
         <v>255550</v>
       </c>
       <c r="J81" s="18">
-        <v>34690720.8375</v>
+        <v>0</v>
       </c>
       <c r="K81" s="17">
-        <v>9.67512323</v>
+        <v>0</v>
       </c>
       <c r="L81" s="11"/>
       <c r="M81" s="17"/>
@@ -3776,10 +3776,10 @@
         <v>26853</v>
       </c>
       <c r="J82" s="18">
-        <v>1773372.12</v>
+        <v>0</v>
       </c>
       <c r="K82" s="17">
-        <v>0.49458741</v>
+        <v>0</v>
       </c>
       <c r="L82" s="11"/>
       <c r="M82" s="17"/>
@@ -3818,10 +3818,10 @@
         <v>61335</v>
       </c>
       <c r="J83" s="18">
-        <v>9923389.65</v>
+        <v>0</v>
       </c>
       <c r="K83" s="17">
-        <v>2.76759939</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11"/>
       <c r="M83" s="17"/>
@@ -3862,10 +3862,10 @@
         <v>449902</v>
       </c>
       <c r="J84" s="18">
-        <v>3599216</v>
+        <v>0</v>
       </c>
       <c r="K84" s="17">
-        <v>1.00380902</v>
+        <v>0</v>
       </c>
       <c r="L84" s="11"/>
       <c r="M84" s="17"/>
@@ -3904,10 +3904,10 @@
         <v>668187</v>
       </c>
       <c r="J85" s="18">
-        <v>5345496</v>
+        <v>0</v>
       </c>
       <c r="K85" s="17">
-        <v>1.49084053</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11"/>
       <c r="M85" s="17"/>
@@ -3946,10 +3946,10 @@
         <v>63699</v>
       </c>
       <c r="J86" s="18">
-        <v>127398</v>
+        <v>0</v>
       </c>
       <c r="K86" s="17">
-        <v>0.03553087</v>
+        <v>0</v>
       </c>
       <c r="L86" s="11"/>
       <c r="M86" s="17"/>
@@ -4025,7 +4025,7 @@
         <v>63</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -4068,10 +4068,10 @@
         <v>5500</v>
       </c>
       <c r="J90" s="18">
-        <v>2277976.8</v>
+        <v>0</v>
       </c>
       <c r="K90" s="17">
-        <v>0.63531993</v>
+        <v>0</v>
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="17"/>
@@ -4108,10 +4108,10 @@
         <v>255550</v>
       </c>
       <c r="J91" s="18">
-        <v>61584381.18</v>
+        <v>0</v>
       </c>
       <c r="K91" s="17">
-        <v>17.175673</v>
+        <v>0</v>
       </c>
       <c r="L91" s="11"/>
       <c r="M91" s="17"/>
@@ -4156,10 +4156,10 @@
         <v>277206</v>
       </c>
       <c r="J92" s="18">
-        <v>48009307.14</v>
+        <v>0</v>
       </c>
       <c r="K92" s="17">
-        <v>13.38963134</v>
+        <v>0</v>
       </c>
       <c r="L92" s="11"/>
       <c r="M92" s="17"/>
@@ -4204,10 +4204,10 @@
         <v>26853</v>
       </c>
       <c r="J93" s="18">
-        <v>3335142.6</v>
+        <v>0</v>
       </c>
       <c r="K93" s="17">
-        <v>0.93015985</v>
+        <v>0</v>
       </c>
       <c r="L93" s="11"/>
       <c r="M93" s="17"/>
@@ -4252,10 +4252,10 @@
         <v>26853</v>
       </c>
       <c r="J94" s="18">
-        <v>5735263.74</v>
+        <v>0</v>
       </c>
       <c r="K94" s="17">
-        <v>1.59954542</v>
+        <v>0</v>
       </c>
       <c r="L94" s="11"/>
       <c r="M94" s="17"/>
@@ -4300,10 +4300,10 @@
         <v>449902</v>
       </c>
       <c r="J95" s="18">
-        <v>17546178</v>
+        <v>0</v>
       </c>
       <c r="K95" s="17">
-        <v>4.89356895</v>
+        <v>0</v>
       </c>
       <c r="L95" s="11"/>
       <c r="M95" s="17"/>
@@ -4344,10 +4344,10 @@
         <v>244459</v>
       </c>
       <c r="J96" s="18">
-        <v>3666885</v>
+        <v>0</v>
       </c>
       <c r="K96" s="17">
-        <v>1.02268167</v>
+        <v>0</v>
       </c>
       <c r="L96" s="11"/>
       <c r="M96" s="17"/>
@@ -4386,10 +4386,10 @@
         <v>668187</v>
       </c>
       <c r="J97" s="18">
-        <v>16036488</v>
+        <v>0</v>
       </c>
       <c r="K97" s="17">
-        <v>4.47252158</v>
+        <v>0</v>
       </c>
       <c r="L97" s="11"/>
       <c r="M97" s="17"/>
@@ -4428,10 +4428,10 @@
         <v>63699</v>
       </c>
       <c r="J98" s="18">
-        <v>254796</v>
+        <v>0</v>
       </c>
       <c r="K98" s="17">
-        <v>0.07106173</v>
+        <v>0</v>
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="17"/>
@@ -4470,10 +4470,10 @@
         <v>46759</v>
       </c>
       <c r="J99" s="18">
-        <v>93518</v>
+        <v>0</v>
       </c>
       <c r="K99" s="17">
-        <v>0.02608185</v>
+        <v>0</v>
       </c>
       <c r="L99" s="11"/>
       <c r="M99" s="17"/>
@@ -5063,7 +5063,7 @@
         <v>2.312</v>
       </c>
       <c r="C2" s="52">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="F2">
         <v>21</v>
@@ -5077,7 +5077,7 @@
         <v>8.943</v>
       </c>
       <c r="C3" s="52">
-        <v>0</v>
+        <v>9.726</v>
       </c>
       <c r="F3">
         <v>25</v>
@@ -5091,7 +5091,7 @@
         <v>25.422</v>
       </c>
       <c r="C4" s="52">
-        <v>0</v>
+        <v>9.726</v>
       </c>
       <c r="F4">
         <v>99</v>
@@ -5105,7 +5105,7 @@
         <v>55.025</v>
       </c>
       <c r="C5" s="52">
-        <v>0</v>
+        <v>9.726</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5116,7 +5116,7 @@
         <v>72.816</v>
       </c>
       <c r="C6" s="52">
-        <v>0</v>
+        <v>9.726</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5127,7 +5127,7 @@
         <v>83.726</v>
       </c>
       <c r="C7" s="52">
-        <v>0</v>
+        <v>9.726</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5138,7 +5138,7 @@
         <v>94.537</v>
       </c>
       <c r="C8" s="52">
-        <v>0</v>
+        <v>9.726</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5149,7 +5149,7 @@
         <v>98.81</v>
       </c>
       <c r="C9" s="52">
-        <v>0</v>
+        <v>9.726</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5160,7 +5160,7 @@
         <v>100</v>
       </c>
       <c r="C10" s="52">
-        <v>0</v>
+        <v>9.726</v>
       </c>
     </row>
   </sheetData>

--- a/backend/temp_schedule.xlsx
+++ b/backend/temp_schedule.xlsx
@@ -83,7 +83,7 @@
     <t>NILAI</t>
   </si>
   <si>
-    <t>RP 397.997.000</t>
+    <t>RP 397.997</t>
   </si>
   <si>
     <t>LOKASI</t>
@@ -1694,39 +1694,29 @@
         <v>1999280</v>
       </c>
       <c r="J29" s="18">
-        <v>0</v>
+        <v>1999280</v>
       </c>
       <c r="K29" s="17">
-        <v>0</v>
+        <v>0.557592</v>
       </c>
       <c r="L29" s="11"/>
       <c r="M29" s="20">
-        <v>0.0619547</v>
+        <v>0.06195467</v>
       </c>
       <c r="N29" s="20">
-        <v>0.0619547</v>
+        <v>0.06195467</v>
       </c>
       <c r="O29" s="20">
-        <v>0.0619547</v>
+        <v>0.06195467</v>
       </c>
       <c r="P29" s="20">
-        <v>0.0619547</v>
-      </c>
-      <c r="Q29" s="20">
-        <v>0.0619547</v>
-      </c>
-      <c r="R29" s="20">
-        <v>0.0619547</v>
-      </c>
-      <c r="S29" s="20">
-        <v>0.0619547</v>
-      </c>
-      <c r="T29" s="20">
-        <v>0.0619547</v>
-      </c>
-      <c r="U29" s="20">
-        <v>0.0619547</v>
-      </c>
+        <v>0.06195467</v>
+      </c>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
       <c r="V29" s="11"/>
       <c r="W29" s="19"/>
     </row>
@@ -1802,39 +1792,29 @@
         <v>300000</v>
       </c>
       <c r="J32" s="18">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="K32" s="17">
-        <v>0</v>
+        <v>0.083669</v>
       </c>
       <c r="L32" s="11"/>
       <c r="M32" s="20">
-        <v>0.00929655</v>
+        <v>0.00929656</v>
       </c>
       <c r="N32" s="20">
-        <v>0.00929655</v>
+        <v>0.00929656</v>
       </c>
       <c r="O32" s="20">
-        <v>0.00929655</v>
+        <v>0.00929656</v>
       </c>
       <c r="P32" s="20">
-        <v>0.00929655</v>
-      </c>
-      <c r="Q32" s="20">
-        <v>0.00929655</v>
-      </c>
-      <c r="R32" s="20">
-        <v>0.00929655</v>
-      </c>
-      <c r="S32" s="20">
-        <v>0.00929655</v>
-      </c>
-      <c r="T32" s="20">
-        <v>0.00929655</v>
-      </c>
-      <c r="U32" s="20">
-        <v>0.00929655</v>
-      </c>
+        <v>0.00929656</v>
+      </c>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
       <c r="V32" s="11"/>
       <c r="W32" s="19"/>
     </row>
@@ -1858,39 +1838,29 @@
         <v>150000</v>
       </c>
       <c r="J33" s="18">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="K33" s="17">
-        <v>0</v>
+        <v>0.041834</v>
       </c>
       <c r="L33" s="11"/>
       <c r="M33" s="20">
-        <v>0.00464828</v>
+        <v>0.00464822</v>
       </c>
       <c r="N33" s="20">
-        <v>0.00464828</v>
+        <v>0.00464822</v>
       </c>
       <c r="O33" s="20">
-        <v>0.00464828</v>
+        <v>0.00464822</v>
       </c>
       <c r="P33" s="20">
-        <v>0.00464828</v>
-      </c>
-      <c r="Q33" s="20">
-        <v>0.00464828</v>
-      </c>
-      <c r="R33" s="20">
-        <v>0.00464828</v>
-      </c>
-      <c r="S33" s="20">
-        <v>0.00464828</v>
-      </c>
-      <c r="T33" s="20">
-        <v>0.00464828</v>
-      </c>
-      <c r="U33" s="20">
-        <v>0.00464828</v>
-      </c>
+        <v>0.00464822</v>
+      </c>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
       <c r="V33" s="11"/>
       <c r="W33" s="19"/>
     </row>
@@ -1966,10 +1936,10 @@
         <v>25000</v>
       </c>
       <c r="J36" s="18">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="K36" s="17">
-        <v>0</v>
+        <v>0.034862</v>
       </c>
       <c r="L36" s="11"/>
       <c r="M36" s="20">
@@ -1984,21 +1954,11 @@
       <c r="P36" s="20">
         <v>0.00387356</v>
       </c>
-      <c r="Q36" s="20">
-        <v>0.00387356</v>
-      </c>
-      <c r="R36" s="20">
-        <v>0.00387356</v>
-      </c>
-      <c r="S36" s="20">
-        <v>0.00387356</v>
-      </c>
-      <c r="T36" s="20">
-        <v>0.00387356</v>
-      </c>
-      <c r="U36" s="20">
-        <v>0.00387356</v>
-      </c>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
       <c r="V36" s="11"/>
       <c r="W36" s="19"/>
     </row>
@@ -2022,39 +1982,29 @@
         <v>60000</v>
       </c>
       <c r="J37" s="18">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="K37" s="17">
-        <v>0</v>
+        <v>0.016734</v>
       </c>
       <c r="L37" s="11"/>
       <c r="M37" s="20">
-        <v>0.00185931</v>
+        <v>0.00185933</v>
       </c>
       <c r="N37" s="20">
-        <v>0.00185931</v>
+        <v>0.00185933</v>
       </c>
       <c r="O37" s="20">
-        <v>0.00185931</v>
+        <v>0.00185933</v>
       </c>
       <c r="P37" s="20">
-        <v>0.00185931</v>
-      </c>
-      <c r="Q37" s="20">
-        <v>0.00185931</v>
-      </c>
-      <c r="R37" s="20">
-        <v>0.00185931</v>
-      </c>
-      <c r="S37" s="20">
-        <v>0.00185931</v>
-      </c>
-      <c r="T37" s="20">
-        <v>0.00185931</v>
-      </c>
-      <c r="U37" s="20">
-        <v>0.00185931</v>
-      </c>
+        <v>0.00185933</v>
+      </c>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
       <c r="V37" s="11"/>
       <c r="W37" s="19"/>
     </row>
@@ -2078,39 +2028,29 @@
         <v>68000</v>
       </c>
       <c r="J38" s="18">
-        <v>0</v>
+        <v>340000</v>
       </c>
       <c r="K38" s="17">
-        <v>0</v>
+        <v>0.094825</v>
       </c>
       <c r="L38" s="11"/>
       <c r="M38" s="20">
-        <v>0.01053609</v>
+        <v>0.01053611</v>
       </c>
       <c r="N38" s="20">
-        <v>0.01053609</v>
+        <v>0.01053611</v>
       </c>
       <c r="O38" s="20">
-        <v>0.01053609</v>
+        <v>0.01053611</v>
       </c>
       <c r="P38" s="20">
-        <v>0.01053609</v>
-      </c>
-      <c r="Q38" s="20">
-        <v>0.01053609</v>
-      </c>
-      <c r="R38" s="20">
-        <v>0.01053609</v>
-      </c>
-      <c r="S38" s="20">
-        <v>0.01053609</v>
-      </c>
-      <c r="T38" s="20">
-        <v>0.01053609</v>
-      </c>
-      <c r="U38" s="20">
-        <v>0.01053609</v>
-      </c>
+        <v>0.01053611</v>
+      </c>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
       <c r="V38" s="11"/>
       <c r="W38" s="19"/>
     </row>
@@ -2134,39 +2074,29 @@
         <v>35000</v>
       </c>
       <c r="J39" s="18">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="K39" s="17">
-        <v>0</v>
+        <v>0.048807</v>
       </c>
       <c r="L39" s="11"/>
       <c r="M39" s="20">
-        <v>0.00542299</v>
+        <v>0.005423</v>
       </c>
       <c r="N39" s="20">
-        <v>0.00542299</v>
+        <v>0.005423</v>
       </c>
       <c r="O39" s="20">
-        <v>0.00542299</v>
+        <v>0.005423</v>
       </c>
       <c r="P39" s="20">
-        <v>0.00542299</v>
-      </c>
-      <c r="Q39" s="20">
-        <v>0.00542299</v>
-      </c>
-      <c r="R39" s="20">
-        <v>0.00542299</v>
-      </c>
-      <c r="S39" s="20">
-        <v>0.00542299</v>
-      </c>
-      <c r="T39" s="20">
-        <v>0.00542299</v>
-      </c>
-      <c r="U39" s="20">
-        <v>0.00542299</v>
-      </c>
+        <v>0.005423</v>
+      </c>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
       <c r="V39" s="11"/>
       <c r="W39" s="19"/>
     </row>
@@ -2242,39 +2172,29 @@
         <v>800000</v>
       </c>
       <c r="J42" s="18">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="K42" s="17">
-        <v>0</v>
+        <v>0.223117</v>
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="20">
-        <v>0.02479081</v>
+        <v>0.02479078</v>
       </c>
       <c r="N42" s="20">
-        <v>0.02479081</v>
+        <v>0.02479078</v>
       </c>
       <c r="O42" s="20">
-        <v>0.02479081</v>
+        <v>0.02479078</v>
       </c>
       <c r="P42" s="20">
-        <v>0.02479081</v>
-      </c>
-      <c r="Q42" s="20">
-        <v>0.02479081</v>
-      </c>
-      <c r="R42" s="20">
-        <v>0.02479081</v>
-      </c>
-      <c r="S42" s="20">
-        <v>0.02479081</v>
-      </c>
-      <c r="T42" s="20">
-        <v>0.02479081</v>
-      </c>
-      <c r="U42" s="20">
-        <v>0.02479081</v>
-      </c>
+        <v>0.02479078</v>
+      </c>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
       <c r="V42" s="11"/>
       <c r="W42" s="19"/>
     </row>
@@ -2350,39 +2270,29 @@
         <v>1500000</v>
       </c>
       <c r="J45" s="18">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="K45" s="17">
-        <v>0</v>
+        <v>0.418345</v>
       </c>
       <c r="L45" s="11"/>
       <c r="M45" s="20">
-        <v>0.04648276</v>
+        <v>0.04648278</v>
       </c>
       <c r="N45" s="20">
-        <v>0.04648276</v>
+        <v>0.04648278</v>
       </c>
       <c r="O45" s="20">
-        <v>0.04648276</v>
+        <v>0.04648278</v>
       </c>
       <c r="P45" s="20">
-        <v>0.04648276</v>
-      </c>
-      <c r="Q45" s="20">
-        <v>0.04648276</v>
-      </c>
-      <c r="R45" s="20">
-        <v>0.04648276</v>
-      </c>
-      <c r="S45" s="20">
-        <v>0.04648276</v>
-      </c>
-      <c r="T45" s="20">
-        <v>0.04648276</v>
-      </c>
-      <c r="U45" s="20">
-        <v>0.04648276</v>
-      </c>
+        <v>0.04648278</v>
+      </c>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
       <c r="V45" s="11"/>
       <c r="W45" s="19"/>
     </row>
@@ -2458,14 +2368,14 @@
         <v>85000</v>
       </c>
       <c r="J48" s="18">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="K48" s="17">
-        <v>0</v>
+        <v>0.023706</v>
       </c>
       <c r="L48" s="11"/>
       <c r="M48" s="20">
-        <v>0.02370621</v>
+        <v>0.023706</v>
       </c>
       <c r="N48" s="17"/>
       <c r="O48" s="17"/>
@@ -2498,14 +2408,14 @@
         <v>85000</v>
       </c>
       <c r="J49" s="18">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="K49" s="17">
-        <v>0</v>
+        <v>0.023706</v>
       </c>
       <c r="L49" s="11"/>
       <c r="M49" s="20">
-        <v>0.02370621</v>
+        <v>0.023706</v>
       </c>
       <c r="N49" s="17"/>
       <c r="O49" s="17"/>
@@ -2584,23 +2494,23 @@
         <v>96</v>
       </c>
       <c r="H52" s="17">
-        <v>207.3864</v>
+        <v>215.34</v>
       </c>
       <c r="I52" s="18">
         <v>5500</v>
       </c>
       <c r="J52" s="18">
-        <v>0</v>
+        <v>1184370</v>
       </c>
       <c r="K52" s="17">
-        <v>0</v>
+        <v>0.330317</v>
       </c>
       <c r="L52" s="11"/>
       <c r="M52" s="20">
-        <v>0.15905823</v>
+        <v>0.159058</v>
       </c>
       <c r="N52" s="20">
-        <v>0.15905823</v>
+        <v>0.159058</v>
       </c>
       <c r="O52" s="17"/>
       <c r="P52" s="17"/>
@@ -2626,32 +2536,28 @@
         <v>96</v>
       </c>
       <c r="H53" s="17">
-        <v>207.3864</v>
+        <v>215.34</v>
       </c>
       <c r="I53" s="18">
         <v>255550</v>
       </c>
       <c r="J53" s="18">
-        <v>0</v>
+        <v>55030137</v>
       </c>
       <c r="K53" s="17">
-        <v>0</v>
+        <v>15.347717</v>
       </c>
       <c r="L53" s="11"/>
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
       <c r="O53" s="20">
-        <v>3.6952119</v>
+        <v>3.695212</v>
       </c>
       <c r="P53" s="20">
-        <v>3.6952119</v>
-      </c>
-      <c r="Q53" s="20">
-        <v>3.6952119</v>
-      </c>
-      <c r="R53" s="20">
-        <v>3.6952119</v>
-      </c>
+        <v>3.695212</v>
+      </c>
+      <c r="Q53" s="17"/>
+      <c r="R53" s="17"/>
       <c r="S53" s="17"/>
       <c r="T53" s="17"/>
       <c r="U53" s="17"/>
@@ -2672,32 +2578,28 @@
         <v>99</v>
       </c>
       <c r="H54" s="17">
-        <v>99.96</v>
+        <v>102.06</v>
       </c>
       <c r="I54" s="18">
         <v>26853</v>
       </c>
       <c r="J54" s="18">
-        <v>0</v>
+        <v>2740617.18</v>
       </c>
       <c r="K54" s="17">
-        <v>0</v>
+        <v>0.764349</v>
       </c>
       <c r="L54" s="11"/>
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
       <c r="O54" s="20">
-        <v>0.18715535</v>
+        <v>0.18715525</v>
       </c>
       <c r="P54" s="20">
-        <v>0.18715535</v>
-      </c>
-      <c r="Q54" s="20">
-        <v>0.18715535</v>
-      </c>
-      <c r="R54" s="20">
-        <v>0.18715535</v>
-      </c>
+        <v>0.18715525</v>
+      </c>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
       <c r="S54" s="17"/>
       <c r="T54" s="17"/>
       <c r="U54" s="17"/>
@@ -2724,25 +2626,23 @@
         <v>61335</v>
       </c>
       <c r="J55" s="18">
-        <v>0</v>
+        <v>9363401.1</v>
       </c>
       <c r="K55" s="17">
-        <v>0</v>
+        <v>2.61142</v>
       </c>
       <c r="L55" s="11"/>
       <c r="M55" s="17"/>
       <c r="N55" s="20">
-        <v>0.65285512</v>
+        <v>0.652855</v>
       </c>
       <c r="O55" s="20">
-        <v>0.65285512</v>
+        <v>0.652855</v>
       </c>
       <c r="P55" s="20">
-        <v>0.65285512</v>
-      </c>
-      <c r="Q55" s="20">
-        <v>0.65285512</v>
-      </c>
+        <v>0.652855</v>
+      </c>
+      <c r="Q55" s="17"/>
       <c r="R55" s="17"/>
       <c r="S55" s="17"/>
       <c r="T55" s="17"/>
@@ -2764,7 +2664,7 @@
         <v>102</v>
       </c>
       <c r="H56" s="17">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I56" s="18">
         <v>449902</v>
@@ -2777,10 +2677,10 @@
       </c>
       <c r="L56" s="11"/>
       <c r="M56" s="20">
-        <v>0.75285676</v>
+        <v>0.752857</v>
       </c>
       <c r="N56" s="20">
-        <v>0.75285676</v>
+        <v>0.752857</v>
       </c>
       <c r="O56" s="17"/>
       <c r="P56" s="17"/>
@@ -2812,28 +2712,20 @@
         <v>668187</v>
       </c>
       <c r="J57" s="18">
-        <v>0</v>
+        <v>8018244</v>
       </c>
       <c r="K57" s="17">
-        <v>0</v>
+        <v>2.236261</v>
       </c>
       <c r="L57" s="11"/>
       <c r="M57" s="17"/>
       <c r="N57" s="17"/>
       <c r="O57" s="17"/>
       <c r="P57" s="17"/>
-      <c r="Q57" s="20">
-        <v>0.5590652</v>
-      </c>
-      <c r="R57" s="20">
-        <v>0.5590652</v>
-      </c>
-      <c r="S57" s="20">
-        <v>0.5590652</v>
-      </c>
-      <c r="T57" s="20">
-        <v>0.5590652</v>
-      </c>
+      <c r="Q57" s="17"/>
+      <c r="R57" s="17"/>
+      <c r="S57" s="17"/>
+      <c r="T57" s="17"/>
       <c r="U57" s="17"/>
       <c r="V57" s="11"/>
       <c r="W57" s="19"/>
@@ -2858,28 +2750,20 @@
         <v>63699</v>
       </c>
       <c r="J58" s="18">
-        <v>0</v>
+        <v>191097</v>
       </c>
       <c r="K58" s="17">
-        <v>0</v>
+        <v>0.053296</v>
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="17"/>
       <c r="N58" s="17"/>
       <c r="O58" s="17"/>
       <c r="P58" s="17"/>
-      <c r="Q58" s="20">
-        <v>0.01332407</v>
-      </c>
-      <c r="R58" s="20">
-        <v>0.01332407</v>
-      </c>
-      <c r="S58" s="20">
-        <v>0.01332407</v>
-      </c>
-      <c r="T58" s="20">
-        <v>0.01332407</v>
-      </c>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
       <c r="U58" s="17"/>
       <c r="V58" s="11"/>
       <c r="W58" s="19"/>
@@ -2956,17 +2840,17 @@
         <v>5500</v>
       </c>
       <c r="J61" s="18">
-        <v>0</v>
+        <v>791076</v>
       </c>
       <c r="K61" s="17">
-        <v>0</v>
+        <v>0.220628</v>
       </c>
       <c r="L61" s="11"/>
       <c r="M61" s="20">
-        <v>0.1103142</v>
+        <v>0.110314</v>
       </c>
       <c r="N61" s="20">
-        <v>0.1103142</v>
+        <v>0.110314</v>
       </c>
       <c r="O61" s="17"/>
       <c r="P61" s="17"/>
@@ -2998,26 +2882,22 @@
         <v>255550</v>
       </c>
       <c r="J62" s="18">
-        <v>0</v>
+        <v>36756267.6</v>
       </c>
       <c r="K62" s="17">
-        <v>0</v>
+        <v>10.251197</v>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" s="17"/>
       <c r="N62" s="17"/>
       <c r="O62" s="20">
-        <v>1.70853286</v>
+        <v>1.70853283</v>
       </c>
       <c r="P62" s="20">
-        <v>3.41706572</v>
-      </c>
-      <c r="Q62" s="20">
-        <v>3.41706572</v>
-      </c>
-      <c r="R62" s="20">
-        <v>1.70853285</v>
-      </c>
+        <v>3.41706567</v>
+      </c>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
       <c r="S62" s="17"/>
       <c r="T62" s="17"/>
       <c r="U62" s="17"/>
@@ -3044,26 +2924,22 @@
         <v>26853</v>
       </c>
       <c r="J63" s="18">
-        <v>0</v>
+        <v>1828152.24</v>
       </c>
       <c r="K63" s="17">
-        <v>0</v>
+        <v>0.509865</v>
       </c>
       <c r="L63" s="11"/>
       <c r="M63" s="17"/>
       <c r="N63" s="17"/>
       <c r="O63" s="20">
-        <v>0.12746635</v>
+        <v>0.12746625</v>
       </c>
       <c r="P63" s="20">
-        <v>0.12746635</v>
-      </c>
-      <c r="Q63" s="20">
-        <v>0.12746635</v>
-      </c>
-      <c r="R63" s="20">
-        <v>0.12746635</v>
-      </c>
+        <v>0.12746625</v>
+      </c>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
       <c r="S63" s="17"/>
       <c r="T63" s="17"/>
       <c r="U63" s="17"/>
@@ -3090,10 +2966,10 @@
         <v>61335</v>
       </c>
       <c r="J64" s="18">
-        <v>0</v>
+        <v>6016350.15</v>
       </c>
       <c r="K64" s="17">
-        <v>0</v>
+        <v>1.677939</v>
       </c>
       <c r="L64" s="11"/>
       <c r="M64" s="17"/>
@@ -3106,9 +2982,7 @@
       <c r="P64" s="20">
         <v>0.5159792</v>
       </c>
-      <c r="Q64" s="20">
-        <v>0.13000185</v>
-      </c>
+      <c r="Q64" s="17"/>
       <c r="R64" s="17"/>
       <c r="S64" s="17"/>
       <c r="T64" s="17"/>
@@ -3130,7 +3004,7 @@
         <v>102</v>
       </c>
       <c r="H65" s="17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I65" s="18">
         <v>449902</v>
@@ -3146,7 +3020,7 @@
         <v>0.55015167</v>
       </c>
       <c r="N65" s="20">
-        <v>0.45365735</v>
+        <v>0.45365733</v>
       </c>
       <c r="O65" s="17"/>
       <c r="P65" s="17"/>
@@ -3178,28 +3052,20 @@
         <v>668187</v>
       </c>
       <c r="J66" s="18">
-        <v>0</v>
+        <v>5345496</v>
       </c>
       <c r="K66" s="17">
-        <v>0</v>
+        <v>1.490841</v>
       </c>
       <c r="L66" s="11"/>
       <c r="M66" s="17"/>
       <c r="N66" s="17"/>
       <c r="O66" s="17"/>
       <c r="P66" s="17"/>
-      <c r="Q66" s="20">
-        <v>0.37271013</v>
-      </c>
-      <c r="R66" s="20">
-        <v>0.37271013</v>
-      </c>
-      <c r="S66" s="20">
-        <v>0.37271013</v>
-      </c>
-      <c r="T66" s="20">
-        <v>0.37271013</v>
-      </c>
+      <c r="Q66" s="17"/>
+      <c r="R66" s="17"/>
+      <c r="S66" s="17"/>
+      <c r="T66" s="17"/>
       <c r="U66" s="17"/>
       <c r="V66" s="11"/>
       <c r="W66" s="19"/>
@@ -3224,28 +3090,20 @@
         <v>63699</v>
       </c>
       <c r="J67" s="18">
-        <v>0</v>
+        <v>127398</v>
       </c>
       <c r="K67" s="17">
-        <v>0</v>
+        <v>0.035531</v>
       </c>
       <c r="L67" s="11"/>
       <c r="M67" s="17"/>
       <c r="N67" s="17"/>
       <c r="O67" s="17"/>
       <c r="P67" s="17"/>
-      <c r="Q67" s="20">
-        <v>0.00888272</v>
-      </c>
-      <c r="R67" s="20">
-        <v>0.00888272</v>
-      </c>
-      <c r="S67" s="20">
-        <v>0.00888272</v>
-      </c>
-      <c r="T67" s="20">
-        <v>0.00888272</v>
-      </c>
+      <c r="Q67" s="17"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
+      <c r="T67" s="17"/>
       <c r="U67" s="17"/>
       <c r="V67" s="11"/>
       <c r="W67" s="19"/>
@@ -3350,10 +3208,10 @@
         <v>5500</v>
       </c>
       <c r="J71" s="18">
-        <v>0</v>
+        <v>27609.999999999996</v>
       </c>
       <c r="K71" s="17">
-        <v>0</v>
+        <v>0.0077</v>
       </c>
       <c r="L71" s="11"/>
       <c r="M71" s="17"/>
@@ -3363,9 +3221,7 @@
       <c r="Q71" s="17"/>
       <c r="R71" s="17"/>
       <c r="S71" s="17"/>
-      <c r="T71" s="20">
-        <v>0.00770033</v>
-      </c>
+      <c r="T71" s="17"/>
       <c r="U71" s="17"/>
       <c r="V71" s="11"/>
       <c r="W71" s="19"/>
@@ -3390,10 +3246,10 @@
         <v>255550</v>
       </c>
       <c r="J72" s="18">
-        <v>0</v>
+        <v>1282861</v>
       </c>
       <c r="K72" s="17">
-        <v>0</v>
+        <v>0.357786</v>
       </c>
       <c r="L72" s="11"/>
       <c r="M72" s="17"/>
@@ -3403,12 +3259,8 @@
       <c r="Q72" s="17"/>
       <c r="R72" s="17"/>
       <c r="S72" s="17"/>
-      <c r="T72" s="20">
-        <v>0.23852369</v>
-      </c>
-      <c r="U72" s="20">
-        <v>0.11926185</v>
-      </c>
+      <c r="T72" s="17"/>
+      <c r="U72" s="17"/>
       <c r="V72" s="11"/>
       <c r="W72" s="19"/>
     </row>
@@ -3432,10 +3284,10 @@
         <v>26853</v>
       </c>
       <c r="J73" s="18">
-        <v>0</v>
+        <v>341033.1</v>
       </c>
       <c r="K73" s="17">
-        <v>0</v>
+        <v>0.095113</v>
       </c>
       <c r="L73" s="11"/>
       <c r="M73" s="17"/>
@@ -3445,12 +3297,8 @@
       <c r="Q73" s="17"/>
       <c r="R73" s="17"/>
       <c r="S73" s="17"/>
-      <c r="T73" s="20">
-        <v>0.06340864</v>
-      </c>
-      <c r="U73" s="20">
-        <v>0.03170432</v>
-      </c>
+      <c r="T73" s="17"/>
+      <c r="U73" s="17"/>
       <c r="V73" s="11"/>
       <c r="W73" s="19"/>
     </row>
@@ -3474,10 +3322,10 @@
         <v>61335</v>
       </c>
       <c r="J74" s="18">
-        <v>0</v>
+        <v>122670</v>
       </c>
       <c r="K74" s="17">
-        <v>0</v>
+        <v>0.034212</v>
       </c>
       <c r="L74" s="11"/>
       <c r="M74" s="17"/>
@@ -3487,12 +3335,8 @@
       <c r="Q74" s="17"/>
       <c r="R74" s="17"/>
       <c r="S74" s="17"/>
-      <c r="T74" s="20">
-        <v>0.02280816</v>
-      </c>
-      <c r="U74" s="20">
-        <v>0.01140408</v>
-      </c>
+      <c r="T74" s="17"/>
+      <c r="U74" s="17"/>
       <c r="V74" s="11"/>
       <c r="W74" s="19"/>
     </row>
@@ -3516,10 +3360,10 @@
         <v>449902</v>
       </c>
       <c r="J75" s="18">
-        <v>0</v>
+        <v>899804</v>
       </c>
       <c r="K75" s="17">
-        <v>0</v>
+        <v>0.250952</v>
       </c>
       <c r="L75" s="11"/>
       <c r="M75" s="17"/>
@@ -3529,12 +3373,8 @@
       <c r="Q75" s="17"/>
       <c r="R75" s="17"/>
       <c r="S75" s="17"/>
-      <c r="T75" s="20">
-        <v>0.1673015</v>
-      </c>
-      <c r="U75" s="20">
-        <v>0.08365075</v>
-      </c>
+      <c r="T75" s="17"/>
+      <c r="U75" s="17"/>
       <c r="V75" s="11"/>
       <c r="W75" s="19"/>
     </row>
@@ -3558,10 +3398,10 @@
         <v>63699</v>
       </c>
       <c r="J76" s="18">
-        <v>0</v>
+        <v>127398</v>
       </c>
       <c r="K76" s="17">
-        <v>0</v>
+        <v>0.035531</v>
       </c>
       <c r="L76" s="11"/>
       <c r="M76" s="17"/>
@@ -3571,12 +3411,8 @@
       <c r="Q76" s="17"/>
       <c r="R76" s="17"/>
       <c r="S76" s="17"/>
-      <c r="T76" s="20">
-        <v>0.02368725</v>
-      </c>
-      <c r="U76" s="20">
-        <v>0.01184362</v>
-      </c>
+      <c r="T76" s="17"/>
+      <c r="U76" s="17"/>
       <c r="V76" s="11"/>
       <c r="W76" s="19"/>
     </row>
@@ -3652,14 +3488,14 @@
         <v>97486</v>
       </c>
       <c r="J79" s="18">
-        <v>0</v>
+        <v>1131081.315</v>
       </c>
       <c r="K79" s="17">
-        <v>0</v>
+        <v>0.315455</v>
       </c>
       <c r="L79" s="11"/>
       <c r="M79" s="20">
-        <v>0.31545471</v>
+        <v>0.315455</v>
       </c>
       <c r="N79" s="17"/>
       <c r="O79" s="17"/>
@@ -3686,20 +3522,20 @@
         <v>96</v>
       </c>
       <c r="H80" s="17">
-        <v>135.74925</v>
+        <v>67.874625</v>
       </c>
       <c r="I80" s="18">
         <v>5500</v>
       </c>
       <c r="J80" s="18">
-        <v>0</v>
+        <v>373310.43749999994</v>
       </c>
       <c r="K80" s="17">
-        <v>0</v>
+        <v>0.104115</v>
       </c>
       <c r="L80" s="11"/>
       <c r="M80" s="20">
-        <v>0.20823001</v>
+        <v>0.20823</v>
       </c>
       <c r="N80" s="17"/>
       <c r="O80" s="17"/>
@@ -3726,27 +3562,27 @@
         <v>96</v>
       </c>
       <c r="H81" s="17">
-        <v>135.74925</v>
+        <v>67.874625</v>
       </c>
       <c r="I81" s="18">
         <v>255550</v>
       </c>
       <c r="J81" s="18">
-        <v>0</v>
+        <v>17345360.41875</v>
       </c>
       <c r="K81" s="17">
-        <v>0</v>
+        <v>4.837562</v>
       </c>
       <c r="L81" s="11"/>
       <c r="M81" s="17"/>
       <c r="N81" s="20">
-        <v>1.2093904</v>
+        <v>1.20939038</v>
       </c>
       <c r="O81" s="20">
-        <v>4.7893144</v>
+        <v>4.78931444</v>
       </c>
       <c r="P81" s="20">
-        <v>3.67641843</v>
+        <v>3.67641818</v>
       </c>
       <c r="Q81" s="17"/>
       <c r="R81" s="17"/>
@@ -3770,24 +3606,24 @@
         <v>99</v>
       </c>
       <c r="H82" s="17">
-        <v>66.04</v>
+        <v>33.02</v>
       </c>
       <c r="I82" s="18">
         <v>26853</v>
       </c>
       <c r="J82" s="18">
-        <v>0</v>
+        <v>886686.06</v>
       </c>
       <c r="K82" s="17">
-        <v>0</v>
+        <v>0.247294</v>
       </c>
       <c r="L82" s="11"/>
       <c r="M82" s="17"/>
       <c r="N82" s="20">
-        <v>0.24729371</v>
+        <v>0.2472935</v>
       </c>
       <c r="O82" s="20">
-        <v>0.24729371</v>
+        <v>0.2472935</v>
       </c>
       <c r="P82" s="17"/>
       <c r="Q82" s="17"/>
@@ -3818,25 +3654,19 @@
         <v>61335</v>
       </c>
       <c r="J83" s="18">
-        <v>0</v>
+        <v>9923389.65</v>
       </c>
       <c r="K83" s="17">
-        <v>0</v>
+        <v>2.767599</v>
       </c>
       <c r="L83" s="11"/>
       <c r="M83" s="17"/>
       <c r="N83" s="17"/>
       <c r="O83" s="17"/>
       <c r="P83" s="17"/>
-      <c r="Q83" s="20">
-        <v>0.18450663</v>
-      </c>
-      <c r="R83" s="20">
-        <v>0.34594992</v>
-      </c>
-      <c r="S83" s="20">
-        <v>2.23714284</v>
-      </c>
+      <c r="Q83" s="17"/>
+      <c r="R83" s="17"/>
+      <c r="S83" s="17"/>
       <c r="T83" s="17"/>
       <c r="U83" s="17"/>
       <c r="V83" s="11"/>
@@ -3856,7 +3686,7 @@
         <v>102</v>
       </c>
       <c r="H84" s="17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I84" s="18">
         <v>449902</v>
@@ -3870,10 +3700,10 @@
       <c r="L84" s="11"/>
       <c r="M84" s="17"/>
       <c r="N84" s="20">
-        <v>0.50190451</v>
+        <v>0.5019045</v>
       </c>
       <c r="O84" s="20">
-        <v>0.50190451</v>
+        <v>0.5019045</v>
       </c>
       <c r="P84" s="17"/>
       <c r="Q84" s="17"/>
@@ -3898,16 +3728,16 @@
         <v>76</v>
       </c>
       <c r="H85" s="17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I85" s="18">
         <v>668187</v>
       </c>
       <c r="J85" s="18">
-        <v>0</v>
+        <v>2672748</v>
       </c>
       <c r="K85" s="17">
-        <v>0</v>
+        <v>0.74542</v>
       </c>
       <c r="L85" s="11"/>
       <c r="M85" s="17"/>
@@ -3917,12 +3747,8 @@
       <c r="Q85" s="17"/>
       <c r="R85" s="17"/>
       <c r="S85" s="17"/>
-      <c r="T85" s="20">
-        <v>0.74542027</v>
-      </c>
-      <c r="U85" s="20">
-        <v>0.74542027</v>
-      </c>
+      <c r="T85" s="17"/>
+      <c r="U85" s="17"/>
       <c r="V85" s="11"/>
       <c r="W85" s="19"/>
     </row>
@@ -3940,16 +3766,16 @@
         <v>76</v>
       </c>
       <c r="H86" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="18">
         <v>63699</v>
       </c>
       <c r="J86" s="18">
-        <v>0</v>
+        <v>63699</v>
       </c>
       <c r="K86" s="17">
-        <v>0</v>
+        <v>0.017765</v>
       </c>
       <c r="L86" s="11"/>
       <c r="M86" s="17"/>
@@ -3959,12 +3785,8 @@
       <c r="Q86" s="17"/>
       <c r="R86" s="17"/>
       <c r="S86" s="17"/>
-      <c r="T86" s="20">
-        <v>0.01776544</v>
-      </c>
-      <c r="U86" s="20">
-        <v>0.01776544</v>
-      </c>
+      <c r="T86" s="17"/>
+      <c r="U86" s="17"/>
       <c r="V86" s="11"/>
       <c r="W86" s="19"/>
     </row>
@@ -4025,7 +3847,7 @@
         <v>63</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -4062,21 +3884,21 @@
         <v>96</v>
       </c>
       <c r="H90" s="17">
-        <v>414.1776</v>
+        <v>572.822</v>
       </c>
       <c r="I90" s="18">
         <v>5500</v>
       </c>
       <c r="J90" s="18">
-        <v>0</v>
+        <v>3150521</v>
       </c>
       <c r="K90" s="17">
-        <v>0</v>
+        <v>0.87867</v>
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="17"/>
       <c r="N90" s="20">
-        <v>0.63531993</v>
+        <v>0.63532</v>
       </c>
       <c r="O90" s="17"/>
       <c r="P90" s="17"/>
@@ -4102,16 +3924,16 @@
         <v>96</v>
       </c>
       <c r="H91" s="17">
-        <v>240.9876</v>
+        <v>297.18</v>
       </c>
       <c r="I91" s="18">
         <v>255550</v>
       </c>
       <c r="J91" s="18">
-        <v>0</v>
+        <v>75944349</v>
       </c>
       <c r="K91" s="17">
-        <v>0</v>
+        <v>21.180619</v>
       </c>
       <c r="L91" s="11"/>
       <c r="M91" s="17"/>
@@ -4122,15 +3944,9 @@
       <c r="P91" s="20">
         <v>5.18136414</v>
       </c>
-      <c r="Q91" s="20">
-        <v>4.29391825</v>
-      </c>
-      <c r="R91" s="20">
-        <v>3.37309326</v>
-      </c>
-      <c r="S91" s="20">
-        <v>3.37309329</v>
-      </c>
+      <c r="Q91" s="17"/>
+      <c r="R91" s="17"/>
+      <c r="S91" s="17"/>
       <c r="T91" s="17"/>
       <c r="U91" s="17"/>
       <c r="V91" s="11"/>
@@ -4150,35 +3966,29 @@
         <v>96</v>
       </c>
       <c r="H92" s="17">
-        <v>173.19</v>
+        <v>275.642</v>
       </c>
       <c r="I92" s="18">
         <v>277206</v>
       </c>
       <c r="J92" s="18">
-        <v>0</v>
+        <v>76409616.252</v>
       </c>
       <c r="K92" s="17">
-        <v>0</v>
+        <v>21.31038</v>
       </c>
       <c r="L92" s="11"/>
       <c r="M92" s="17"/>
       <c r="N92" s="17"/>
       <c r="O92" s="20">
-        <v>0.74386841</v>
+        <v>0.74386839</v>
       </c>
       <c r="P92" s="20">
-        <v>9.23160521</v>
-      </c>
-      <c r="Q92" s="20">
-        <v>3.34740784</v>
-      </c>
-      <c r="R92" s="20">
-        <v>0.03337494</v>
-      </c>
-      <c r="S92" s="20">
-        <v>0.03337494</v>
-      </c>
+        <v>9.23160522</v>
+      </c>
+      <c r="Q92" s="17"/>
+      <c r="R92" s="17"/>
+      <c r="S92" s="17"/>
       <c r="T92" s="17"/>
       <c r="U92" s="17"/>
       <c r="V92" s="11"/>
@@ -4198,35 +4008,29 @@
         <v>99</v>
       </c>
       <c r="H93" s="17">
-        <v>124.2</v>
+        <v>154.2</v>
       </c>
       <c r="I93" s="18">
         <v>26853</v>
       </c>
       <c r="J93" s="18">
-        <v>0</v>
+        <v>4140732.5999999996</v>
       </c>
       <c r="K93" s="17">
-        <v>0</v>
+        <v>1.154836</v>
       </c>
       <c r="L93" s="11"/>
       <c r="M93" s="17"/>
       <c r="N93" s="17"/>
       <c r="O93" s="20">
-        <v>0.15502664</v>
+        <v>0.15502667</v>
       </c>
       <c r="P93" s="20">
-        <v>0.31005328</v>
-      </c>
-      <c r="Q93" s="20">
-        <v>0.23253996</v>
-      </c>
-      <c r="R93" s="20">
-        <v>0.11626999</v>
-      </c>
-      <c r="S93" s="20">
-        <v>0.11626999</v>
-      </c>
+        <v>0.31005333</v>
+      </c>
+      <c r="Q93" s="17"/>
+      <c r="R93" s="17"/>
+      <c r="S93" s="17"/>
       <c r="T93" s="17"/>
       <c r="U93" s="17"/>
       <c r="V93" s="11"/>
@@ -4246,35 +4050,29 @@
         <v>99</v>
       </c>
       <c r="H94" s="17">
-        <v>213.58</v>
+        <v>267.6554554</v>
       </c>
       <c r="I94" s="18">
         <v>26853</v>
       </c>
       <c r="J94" s="18">
-        <v>0</v>
+        <v>7187351.9438562</v>
       </c>
       <c r="K94" s="17">
-        <v>0</v>
+        <v>2.004528</v>
       </c>
       <c r="L94" s="11"/>
       <c r="M94" s="17"/>
       <c r="N94" s="17"/>
       <c r="O94" s="20">
-        <v>0.39988636</v>
+        <v>0.39988625</v>
       </c>
       <c r="P94" s="20">
-        <v>0.39988636</v>
-      </c>
-      <c r="Q94" s="20">
-        <v>0.39988636</v>
-      </c>
-      <c r="R94" s="20">
-        <v>0.19994317</v>
-      </c>
-      <c r="S94" s="20">
-        <v>0.19994317</v>
-      </c>
+        <v>0.39988625</v>
+      </c>
+      <c r="Q94" s="17"/>
+      <c r="R94" s="17"/>
+      <c r="S94" s="17"/>
       <c r="T94" s="17"/>
       <c r="U94" s="17"/>
       <c r="V94" s="11"/>
@@ -4294,27 +4092,27 @@
         <v>102</v>
       </c>
       <c r="H95" s="17">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I95" s="18">
         <v>449902</v>
       </c>
       <c r="J95" s="18">
-        <v>0</v>
+        <v>6298628</v>
       </c>
       <c r="K95" s="17">
-        <v>0</v>
+        <v>1.756666</v>
       </c>
       <c r="L95" s="11"/>
       <c r="M95" s="17"/>
       <c r="N95" s="20">
-        <v>1.22339224</v>
+        <v>1.22339225</v>
       </c>
       <c r="O95" s="20">
-        <v>1.63118965</v>
+        <v>1.63118967</v>
       </c>
       <c r="P95" s="20">
-        <v>2.03898706</v>
+        <v>2.03898708</v>
       </c>
       <c r="Q95" s="17"/>
       <c r="R95" s="17"/>
@@ -4338,16 +4136,16 @@
         <v>76</v>
       </c>
       <c r="H96" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I96" s="18">
         <v>244459</v>
       </c>
       <c r="J96" s="18">
-        <v>0</v>
+        <v>3422426</v>
       </c>
       <c r="K96" s="17">
-        <v>0</v>
+        <v>0.954503</v>
       </c>
       <c r="L96" s="11"/>
       <c r="M96" s="17"/>
@@ -4356,12 +4154,8 @@
       <c r="P96" s="17"/>
       <c r="Q96" s="17"/>
       <c r="R96" s="17"/>
-      <c r="S96" s="20">
-        <v>0.68178778</v>
-      </c>
-      <c r="T96" s="20">
-        <v>0.34089389</v>
-      </c>
+      <c r="S96" s="17"/>
+      <c r="T96" s="17"/>
       <c r="U96" s="17"/>
       <c r="V96" s="11"/>
       <c r="W96" s="19"/>
@@ -4380,16 +4174,16 @@
         <v>76</v>
       </c>
       <c r="H97" s="17">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I97" s="18">
         <v>668187</v>
       </c>
       <c r="J97" s="18">
-        <v>0</v>
+        <v>13363740</v>
       </c>
       <c r="K97" s="17">
-        <v>0</v>
+        <v>3.727101</v>
       </c>
       <c r="L97" s="11"/>
       <c r="M97" s="17"/>
@@ -4398,12 +4192,8 @@
       <c r="P97" s="17"/>
       <c r="Q97" s="17"/>
       <c r="R97" s="17"/>
-      <c r="S97" s="20">
-        <v>2.98168105</v>
-      </c>
-      <c r="T97" s="20">
-        <v>1.49084053</v>
-      </c>
+      <c r="S97" s="17"/>
+      <c r="T97" s="17"/>
       <c r="U97" s="17"/>
       <c r="V97" s="11"/>
       <c r="W97" s="19"/>
@@ -4422,16 +4212,16 @@
         <v>76</v>
       </c>
       <c r="H98" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I98" s="18">
         <v>63699</v>
       </c>
       <c r="J98" s="18">
-        <v>0</v>
+        <v>382194</v>
       </c>
       <c r="K98" s="17">
-        <v>0</v>
+        <v>0.106593</v>
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="17"/>
@@ -4440,12 +4230,8 @@
       <c r="P98" s="17"/>
       <c r="Q98" s="17"/>
       <c r="R98" s="17"/>
-      <c r="S98" s="20">
-        <v>0.04737449</v>
-      </c>
-      <c r="T98" s="20">
-        <v>0.02368724</v>
-      </c>
+      <c r="S98" s="17"/>
+      <c r="T98" s="17"/>
       <c r="U98" s="17"/>
       <c r="V98" s="11"/>
       <c r="W98" s="19"/>
@@ -4464,16 +4250,16 @@
         <v>76</v>
       </c>
       <c r="H99" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" s="18">
         <v>46759</v>
       </c>
       <c r="J99" s="18">
-        <v>0</v>
+        <v>46759</v>
       </c>
       <c r="K99" s="17">
-        <v>0</v>
+        <v>0.013041</v>
       </c>
       <c r="L99" s="11"/>
       <c r="M99" s="17"/>
@@ -4482,12 +4268,8 @@
       <c r="P99" s="17"/>
       <c r="Q99" s="17"/>
       <c r="R99" s="17"/>
-      <c r="S99" s="20">
-        <v>0.0173879</v>
-      </c>
-      <c r="T99" s="20">
-        <v>0.00869395</v>
-      </c>
+      <c r="S99" s="17"/>
+      <c r="T99" s="17"/>
       <c r="U99" s="17"/>
       <c r="V99" s="11"/>
       <c r="W99" s="19"/>
@@ -5063,7 +4845,7 @@
         <v>2.312</v>
       </c>
       <c r="C2" s="52">
-        <v>7.06</v>
+        <v>7.252</v>
       </c>
       <c r="F2">
         <v>21</v>
@@ -5077,7 +4859,7 @@
         <v>8.943</v>
       </c>
       <c r="C3" s="52">
-        <v>9.726</v>
+        <v>10.05</v>
       </c>
       <c r="F3">
         <v>25</v>
@@ -5091,7 +4873,7 @@
         <v>25.422</v>
       </c>
       <c r="C4" s="52">
-        <v>9.726</v>
+        <v>28.684</v>
       </c>
       <c r="F4">
         <v>99</v>
@@ -5105,7 +4887,7 @@
         <v>55.025</v>
       </c>
       <c r="C5" s="52">
-        <v>9.726</v>
+        <v>77.035</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5113,10 +4895,10 @@
         <v>150</v>
       </c>
       <c r="B6" s="52">
-        <v>72.816</v>
+        <v>55.025</v>
       </c>
       <c r="C6" s="52">
-        <v>9.726</v>
+        <v>73.061</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5124,10 +4906,10 @@
         <v>151</v>
       </c>
       <c r="B7" s="52">
-        <v>83.726</v>
+        <v>55.025</v>
       </c>
       <c r="C7" s="52">
-        <v>9.726</v>
+        <v>73.061</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5135,10 +4917,10 @@
         <v>152</v>
       </c>
       <c r="B8" s="52">
-        <v>94.537</v>
+        <v>55.025</v>
       </c>
       <c r="C8" s="52">
-        <v>9.726</v>
+        <v>73.061</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5146,10 +4928,10 @@
         <v>153</v>
       </c>
       <c r="B9" s="52">
-        <v>98.81</v>
+        <v>55.025</v>
       </c>
       <c r="C9" s="52">
-        <v>9.726</v>
+        <v>73.061</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5157,10 +4939,10 @@
         <v>154</v>
       </c>
       <c r="B10" s="52">
-        <v>100</v>
+        <v>55.025</v>
       </c>
       <c r="C10" s="52">
-        <v>9.726</v>
+        <v>73.061</v>
       </c>
     </row>
   </sheetData>

--- a/backend/temp_schedule.xlsx
+++ b/backend/temp_schedule.xlsx
@@ -602,20 +602,6 @@
     </border>
     <border>
       <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom style="thin"/>
@@ -635,11 +621,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -723,33 +723,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -759,7 +750,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,7 +1106,7 @@
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="5" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
     <col min="13" max="21" width="15" customWidth="1"/>
     <col min="22" max="22" width="6" customWidth="1"/>
     <col min="23" max="23" width="15" customWidth="1"/>
@@ -1712,11 +1704,21 @@
       <c r="P29" s="20">
         <v>0.06195467</v>
       </c>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
+      <c r="Q29" s="20">
+        <v>0.06195467</v>
+      </c>
+      <c r="R29" s="20">
+        <v>0.06195467</v>
+      </c>
+      <c r="S29" s="20">
+        <v>0.06195467</v>
+      </c>
+      <c r="T29" s="20">
+        <v>0.06195467</v>
+      </c>
+      <c r="U29" s="20">
+        <v>0.06195467</v>
+      </c>
       <c r="V29" s="11"/>
       <c r="W29" s="19"/>
     </row>
@@ -1810,11 +1812,21 @@
       <c r="P32" s="20">
         <v>0.00929656</v>
       </c>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
+      <c r="Q32" s="20">
+        <v>0.00929656</v>
+      </c>
+      <c r="R32" s="20">
+        <v>0.00929656</v>
+      </c>
+      <c r="S32" s="20">
+        <v>0.00929656</v>
+      </c>
+      <c r="T32" s="20">
+        <v>0.00929656</v>
+      </c>
+      <c r="U32" s="20">
+        <v>0.00929656</v>
+      </c>
       <c r="V32" s="11"/>
       <c r="W32" s="19"/>
     </row>
@@ -1856,11 +1868,21 @@
       <c r="P33" s="20">
         <v>0.00464822</v>
       </c>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
+      <c r="Q33" s="20">
+        <v>0.00464822</v>
+      </c>
+      <c r="R33" s="20">
+        <v>0.00464822</v>
+      </c>
+      <c r="S33" s="20">
+        <v>0.00464822</v>
+      </c>
+      <c r="T33" s="20">
+        <v>0.00464822</v>
+      </c>
+      <c r="U33" s="20">
+        <v>0.00464822</v>
+      </c>
       <c r="V33" s="11"/>
       <c r="W33" s="19"/>
     </row>
@@ -1954,11 +1976,21 @@
       <c r="P36" s="20">
         <v>0.00387356</v>
       </c>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="17"/>
-      <c r="U36" s="17"/>
+      <c r="Q36" s="20">
+        <v>0.00387356</v>
+      </c>
+      <c r="R36" s="20">
+        <v>0.00387356</v>
+      </c>
+      <c r="S36" s="20">
+        <v>0.00387356</v>
+      </c>
+      <c r="T36" s="20">
+        <v>0.00387356</v>
+      </c>
+      <c r="U36" s="20">
+        <v>0.00387356</v>
+      </c>
       <c r="V36" s="11"/>
       <c r="W36" s="19"/>
     </row>
@@ -2000,11 +2032,21 @@
       <c r="P37" s="20">
         <v>0.00185933</v>
       </c>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
+      <c r="Q37" s="20">
+        <v>0.00185933</v>
+      </c>
+      <c r="R37" s="20">
+        <v>0.00185933</v>
+      </c>
+      <c r="S37" s="20">
+        <v>0.00185933</v>
+      </c>
+      <c r="T37" s="20">
+        <v>0.00185933</v>
+      </c>
+      <c r="U37" s="20">
+        <v>0.00185933</v>
+      </c>
       <c r="V37" s="11"/>
       <c r="W37" s="19"/>
     </row>
@@ -2046,11 +2088,21 @@
       <c r="P38" s="20">
         <v>0.01053611</v>
       </c>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17"/>
+      <c r="Q38" s="20">
+        <v>0.01053611</v>
+      </c>
+      <c r="R38" s="20">
+        <v>0.01053611</v>
+      </c>
+      <c r="S38" s="20">
+        <v>0.01053611</v>
+      </c>
+      <c r="T38" s="20">
+        <v>0.01053611</v>
+      </c>
+      <c r="U38" s="20">
+        <v>0.01053611</v>
+      </c>
       <c r="V38" s="11"/>
       <c r="W38" s="19"/>
     </row>
@@ -2092,11 +2144,21 @@
       <c r="P39" s="20">
         <v>0.005423</v>
       </c>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-      <c r="T39" s="17"/>
-      <c r="U39" s="17"/>
+      <c r="Q39" s="20">
+        <v>0.005423</v>
+      </c>
+      <c r="R39" s="20">
+        <v>0.005423</v>
+      </c>
+      <c r="S39" s="20">
+        <v>0.005423</v>
+      </c>
+      <c r="T39" s="20">
+        <v>0.005423</v>
+      </c>
+      <c r="U39" s="20">
+        <v>0.005423</v>
+      </c>
       <c r="V39" s="11"/>
       <c r="W39" s="19"/>
     </row>
@@ -2190,11 +2252,21 @@
       <c r="P42" s="20">
         <v>0.02479078</v>
       </c>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
+      <c r="Q42" s="20">
+        <v>0.02479078</v>
+      </c>
+      <c r="R42" s="20">
+        <v>0.02479078</v>
+      </c>
+      <c r="S42" s="20">
+        <v>0.02479078</v>
+      </c>
+      <c r="T42" s="20">
+        <v>0.02479078</v>
+      </c>
+      <c r="U42" s="20">
+        <v>0.02479078</v>
+      </c>
       <c r="V42" s="11"/>
       <c r="W42" s="19"/>
     </row>
@@ -2288,11 +2360,21 @@
       <c r="P45" s="20">
         <v>0.04648278</v>
       </c>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
+      <c r="Q45" s="20">
+        <v>0.04648278</v>
+      </c>
+      <c r="R45" s="20">
+        <v>0.04648278</v>
+      </c>
+      <c r="S45" s="20">
+        <v>0.04648278</v>
+      </c>
+      <c r="T45" s="20">
+        <v>0.04648278</v>
+      </c>
+      <c r="U45" s="20">
+        <v>0.04648278</v>
+      </c>
       <c r="V45" s="11"/>
       <c r="W45" s="19"/>
     </row>
@@ -2494,16 +2576,16 @@
         <v>96</v>
       </c>
       <c r="H52" s="17">
-        <v>215.34</v>
+        <v>207.3864</v>
       </c>
       <c r="I52" s="18">
         <v>5500</v>
       </c>
       <c r="J52" s="18">
-        <v>1184370</v>
+        <v>1140625.2</v>
       </c>
       <c r="K52" s="17">
-        <v>0.330317</v>
+        <v>0.318116</v>
       </c>
       <c r="L52" s="11"/>
       <c r="M52" s="20">
@@ -2536,16 +2618,16 @@
         <v>96</v>
       </c>
       <c r="H53" s="17">
-        <v>215.34</v>
+        <v>207.3864</v>
       </c>
       <c r="I53" s="18">
         <v>255550</v>
       </c>
       <c r="J53" s="18">
-        <v>55030137</v>
+        <v>52997594.52</v>
       </c>
       <c r="K53" s="17">
-        <v>15.347717</v>
+        <v>14.780848</v>
       </c>
       <c r="L53" s="11"/>
       <c r="M53" s="17"/>
@@ -2556,8 +2638,12 @@
       <c r="P53" s="20">
         <v>3.695212</v>
       </c>
-      <c r="Q53" s="17"/>
-      <c r="R53" s="17"/>
+      <c r="Q53" s="20">
+        <v>3.695212</v>
+      </c>
+      <c r="R53" s="20">
+        <v>3.695212</v>
+      </c>
       <c r="S53" s="17"/>
       <c r="T53" s="17"/>
       <c r="U53" s="17"/>
@@ -2578,16 +2664,16 @@
         <v>99</v>
       </c>
       <c r="H54" s="17">
-        <v>102.06</v>
+        <v>99.96</v>
       </c>
       <c r="I54" s="18">
         <v>26853</v>
       </c>
       <c r="J54" s="18">
-        <v>2740617.18</v>
+        <v>2684225.88</v>
       </c>
       <c r="K54" s="17">
-        <v>0.764349</v>
+        <v>0.748621</v>
       </c>
       <c r="L54" s="11"/>
       <c r="M54" s="17"/>
@@ -2598,8 +2684,12 @@
       <c r="P54" s="20">
         <v>0.18715525</v>
       </c>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17"/>
+      <c r="Q54" s="20">
+        <v>0.18715525</v>
+      </c>
+      <c r="R54" s="20">
+        <v>0.18715525</v>
+      </c>
       <c r="S54" s="17"/>
       <c r="T54" s="17"/>
       <c r="U54" s="17"/>
@@ -2642,7 +2732,9 @@
       <c r="P55" s="20">
         <v>0.652855</v>
       </c>
-      <c r="Q55" s="17"/>
+      <c r="Q55" s="20">
+        <v>0.652855</v>
+      </c>
       <c r="R55" s="17"/>
       <c r="S55" s="17"/>
       <c r="T55" s="17"/>
@@ -2664,16 +2756,16 @@
         <v>102</v>
       </c>
       <c r="H56" s="17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I56" s="18">
         <v>449902</v>
       </c>
       <c r="J56" s="18">
-        <v>0</v>
+        <v>5398824</v>
       </c>
       <c r="K56" s="17">
-        <v>0</v>
+        <v>1.505714</v>
       </c>
       <c r="L56" s="11"/>
       <c r="M56" s="20">
@@ -2722,10 +2814,18 @@
       <c r="N57" s="17"/>
       <c r="O57" s="17"/>
       <c r="P57" s="17"/>
-      <c r="Q57" s="17"/>
-      <c r="R57" s="17"/>
-      <c r="S57" s="17"/>
-      <c r="T57" s="17"/>
+      <c r="Q57" s="20">
+        <v>0.55906525</v>
+      </c>
+      <c r="R57" s="20">
+        <v>0.55906525</v>
+      </c>
+      <c r="S57" s="20">
+        <v>0.55906525</v>
+      </c>
+      <c r="T57" s="20">
+        <v>0.55906525</v>
+      </c>
       <c r="U57" s="17"/>
       <c r="V57" s="11"/>
       <c r="W57" s="19"/>
@@ -2760,10 +2860,18 @@
       <c r="N58" s="17"/>
       <c r="O58" s="17"/>
       <c r="P58" s="17"/>
-      <c r="Q58" s="17"/>
-      <c r="R58" s="17"/>
-      <c r="S58" s="17"/>
-      <c r="T58" s="17"/>
+      <c r="Q58" s="20">
+        <v>0.013324</v>
+      </c>
+      <c r="R58" s="20">
+        <v>0.013324</v>
+      </c>
+      <c r="S58" s="20">
+        <v>0.013324</v>
+      </c>
+      <c r="T58" s="20">
+        <v>0.013324</v>
+      </c>
       <c r="U58" s="17"/>
       <c r="V58" s="11"/>
       <c r="W58" s="19"/>
@@ -2896,8 +3004,12 @@
       <c r="P62" s="20">
         <v>3.41706567</v>
       </c>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17"/>
+      <c r="Q62" s="20">
+        <v>3.41706567</v>
+      </c>
+      <c r="R62" s="20">
+        <v>1.70853283</v>
+      </c>
       <c r="S62" s="17"/>
       <c r="T62" s="17"/>
       <c r="U62" s="17"/>
@@ -2938,8 +3050,12 @@
       <c r="P63" s="20">
         <v>0.12746625</v>
       </c>
-      <c r="Q63" s="17"/>
-      <c r="R63" s="17"/>
+      <c r="Q63" s="20">
+        <v>0.12746625</v>
+      </c>
+      <c r="R63" s="20">
+        <v>0.12746625</v>
+      </c>
       <c r="S63" s="17"/>
       <c r="T63" s="17"/>
       <c r="U63" s="17"/>
@@ -2982,7 +3098,9 @@
       <c r="P64" s="20">
         <v>0.5159792</v>
       </c>
-      <c r="Q64" s="17"/>
+      <c r="Q64" s="20">
+        <v>0.1300014</v>
+      </c>
       <c r="R64" s="17"/>
       <c r="S64" s="17"/>
       <c r="T64" s="17"/>
@@ -3004,16 +3122,16 @@
         <v>102</v>
       </c>
       <c r="H65" s="17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I65" s="18">
         <v>449902</v>
       </c>
       <c r="J65" s="18">
-        <v>0</v>
+        <v>3599216</v>
       </c>
       <c r="K65" s="17">
-        <v>0</v>
+        <v>1.003809</v>
       </c>
       <c r="L65" s="11"/>
       <c r="M65" s="20">
@@ -3062,10 +3180,18 @@
       <c r="N66" s="17"/>
       <c r="O66" s="17"/>
       <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17"/>
-      <c r="S66" s="17"/>
-      <c r="T66" s="17"/>
+      <c r="Q66" s="20">
+        <v>0.37271025</v>
+      </c>
+      <c r="R66" s="20">
+        <v>0.37271025</v>
+      </c>
+      <c r="S66" s="20">
+        <v>0.37271025</v>
+      </c>
+      <c r="T66" s="20">
+        <v>0.37271025</v>
+      </c>
       <c r="U66" s="17"/>
       <c r="V66" s="11"/>
       <c r="W66" s="19"/>
@@ -3100,10 +3226,18 @@
       <c r="N67" s="17"/>
       <c r="O67" s="17"/>
       <c r="P67" s="17"/>
-      <c r="Q67" s="17"/>
-      <c r="R67" s="17"/>
-      <c r="S67" s="17"/>
-      <c r="T67" s="17"/>
+      <c r="Q67" s="20">
+        <v>0.00888275</v>
+      </c>
+      <c r="R67" s="20">
+        <v>0.00888275</v>
+      </c>
+      <c r="S67" s="20">
+        <v>0.00888275</v>
+      </c>
+      <c r="T67" s="20">
+        <v>0.00888275</v>
+      </c>
       <c r="U67" s="17"/>
       <c r="V67" s="11"/>
       <c r="W67" s="19"/>
@@ -3221,7 +3355,9 @@
       <c r="Q71" s="17"/>
       <c r="R71" s="17"/>
       <c r="S71" s="17"/>
-      <c r="T71" s="17"/>
+      <c r="T71" s="20">
+        <v>0.0077</v>
+      </c>
       <c r="U71" s="17"/>
       <c r="V71" s="11"/>
       <c r="W71" s="19"/>
@@ -3259,8 +3395,12 @@
       <c r="Q72" s="17"/>
       <c r="R72" s="17"/>
       <c r="S72" s="17"/>
-      <c r="T72" s="17"/>
-      <c r="U72" s="17"/>
+      <c r="T72" s="20">
+        <v>0.238524</v>
+      </c>
+      <c r="U72" s="20">
+        <v>0.119262</v>
+      </c>
       <c r="V72" s="11"/>
       <c r="W72" s="19"/>
     </row>
@@ -3297,8 +3437,12 @@
       <c r="Q73" s="17"/>
       <c r="R73" s="17"/>
       <c r="S73" s="17"/>
-      <c r="T73" s="17"/>
-      <c r="U73" s="17"/>
+      <c r="T73" s="20">
+        <v>0.06340867</v>
+      </c>
+      <c r="U73" s="20">
+        <v>0.03170433</v>
+      </c>
       <c r="V73" s="11"/>
       <c r="W73" s="19"/>
     </row>
@@ -3335,8 +3479,12 @@
       <c r="Q74" s="17"/>
       <c r="R74" s="17"/>
       <c r="S74" s="17"/>
-      <c r="T74" s="17"/>
-      <c r="U74" s="17"/>
+      <c r="T74" s="20">
+        <v>0.022808</v>
+      </c>
+      <c r="U74" s="20">
+        <v>0.011404</v>
+      </c>
       <c r="V74" s="11"/>
       <c r="W74" s="19"/>
     </row>
@@ -3373,8 +3521,12 @@
       <c r="Q75" s="17"/>
       <c r="R75" s="17"/>
       <c r="S75" s="17"/>
-      <c r="T75" s="17"/>
-      <c r="U75" s="17"/>
+      <c r="T75" s="20">
+        <v>0.16730133</v>
+      </c>
+      <c r="U75" s="20">
+        <v>0.08365067</v>
+      </c>
       <c r="V75" s="11"/>
       <c r="W75" s="19"/>
     </row>
@@ -3411,8 +3563,12 @@
       <c r="Q76" s="17"/>
       <c r="R76" s="17"/>
       <c r="S76" s="17"/>
-      <c r="T76" s="17"/>
-      <c r="U76" s="17"/>
+      <c r="T76" s="20">
+        <v>0.02368733</v>
+      </c>
+      <c r="U76" s="20">
+        <v>0.01184367</v>
+      </c>
       <c r="V76" s="11"/>
       <c r="W76" s="19"/>
     </row>
@@ -3522,16 +3678,16 @@
         <v>96</v>
       </c>
       <c r="H80" s="17">
-        <v>67.874625</v>
+        <v>135.74925</v>
       </c>
       <c r="I80" s="18">
         <v>5500</v>
       </c>
       <c r="J80" s="18">
-        <v>373310.43749999994</v>
+        <v>746620.8749999999</v>
       </c>
       <c r="K80" s="17">
-        <v>0.104115</v>
+        <v>0.20823</v>
       </c>
       <c r="L80" s="11"/>
       <c r="M80" s="20">
@@ -3562,16 +3718,16 @@
         <v>96</v>
       </c>
       <c r="H81" s="17">
-        <v>67.874625</v>
+        <v>135.74925</v>
       </c>
       <c r="I81" s="18">
         <v>255550</v>
       </c>
       <c r="J81" s="18">
-        <v>17345360.41875</v>
+        <v>34690720.8375</v>
       </c>
       <c r="K81" s="17">
-        <v>4.837562</v>
+        <v>9.675123</v>
       </c>
       <c r="L81" s="11"/>
       <c r="M81" s="17"/>
@@ -3606,16 +3762,16 @@
         <v>99</v>
       </c>
       <c r="H82" s="17">
-        <v>33.02</v>
+        <v>66.04</v>
       </c>
       <c r="I82" s="18">
         <v>26853</v>
       </c>
       <c r="J82" s="18">
-        <v>886686.06</v>
+        <v>1773372.12</v>
       </c>
       <c r="K82" s="17">
-        <v>0.247294</v>
+        <v>0.494587</v>
       </c>
       <c r="L82" s="11"/>
       <c r="M82" s="17"/>
@@ -3664,9 +3820,15 @@
       <c r="N83" s="17"/>
       <c r="O83" s="17"/>
       <c r="P83" s="17"/>
-      <c r="Q83" s="17"/>
-      <c r="R83" s="17"/>
-      <c r="S83" s="17"/>
+      <c r="Q83" s="20">
+        <v>0.1845066</v>
+      </c>
+      <c r="R83" s="20">
+        <v>0.34594988</v>
+      </c>
+      <c r="S83" s="20">
+        <v>2.23714252</v>
+      </c>
       <c r="T83" s="17"/>
       <c r="U83" s="17"/>
       <c r="V83" s="11"/>
@@ -3686,16 +3848,16 @@
         <v>102</v>
       </c>
       <c r="H84" s="17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I84" s="18">
         <v>449902</v>
       </c>
       <c r="J84" s="18">
-        <v>0</v>
+        <v>3599216</v>
       </c>
       <c r="K84" s="17">
-        <v>0</v>
+        <v>1.003809</v>
       </c>
       <c r="L84" s="11"/>
       <c r="M84" s="17"/>
@@ -3728,16 +3890,16 @@
         <v>76</v>
       </c>
       <c r="H85" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I85" s="18">
         <v>668187</v>
       </c>
       <c r="J85" s="18">
-        <v>2672748</v>
+        <v>5345496</v>
       </c>
       <c r="K85" s="17">
-        <v>0.74542</v>
+        <v>1.490841</v>
       </c>
       <c r="L85" s="11"/>
       <c r="M85" s="17"/>
@@ -3747,8 +3909,12 @@
       <c r="Q85" s="17"/>
       <c r="R85" s="17"/>
       <c r="S85" s="17"/>
-      <c r="T85" s="17"/>
-      <c r="U85" s="17"/>
+      <c r="T85" s="20">
+        <v>0.7454205</v>
+      </c>
+      <c r="U85" s="20">
+        <v>0.7454205</v>
+      </c>
       <c r="V85" s="11"/>
       <c r="W85" s="19"/>
     </row>
@@ -3766,16 +3932,16 @@
         <v>76</v>
       </c>
       <c r="H86" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I86" s="18">
         <v>63699</v>
       </c>
       <c r="J86" s="18">
-        <v>63699</v>
+        <v>127398</v>
       </c>
       <c r="K86" s="17">
-        <v>0.017765</v>
+        <v>0.035531</v>
       </c>
       <c r="L86" s="11"/>
       <c r="M86" s="17"/>
@@ -3785,8 +3951,12 @@
       <c r="Q86" s="17"/>
       <c r="R86" s="17"/>
       <c r="S86" s="17"/>
-      <c r="T86" s="17"/>
-      <c r="U86" s="17"/>
+      <c r="T86" s="20">
+        <v>0.0177655</v>
+      </c>
+      <c r="U86" s="20">
+        <v>0.0177655</v>
+      </c>
       <c r="V86" s="11"/>
       <c r="W86" s="19"/>
     </row>
@@ -3884,16 +4054,16 @@
         <v>96</v>
       </c>
       <c r="H90" s="17">
-        <v>572.822</v>
+        <v>414.1776</v>
       </c>
       <c r="I90" s="18">
         <v>5500</v>
       </c>
       <c r="J90" s="18">
-        <v>3150521</v>
+        <v>2277976.8</v>
       </c>
       <c r="K90" s="17">
-        <v>0.87867</v>
+        <v>0.63532</v>
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="17"/>
@@ -3924,16 +4094,16 @@
         <v>96</v>
       </c>
       <c r="H91" s="17">
-        <v>297.18</v>
+        <v>240.9876</v>
       </c>
       <c r="I91" s="18">
         <v>255550</v>
       </c>
       <c r="J91" s="18">
-        <v>75944349</v>
+        <v>61584381.18</v>
       </c>
       <c r="K91" s="17">
-        <v>21.180619</v>
+        <v>17.175673</v>
       </c>
       <c r="L91" s="11"/>
       <c r="M91" s="17"/>
@@ -3944,9 +4114,15 @@
       <c r="P91" s="20">
         <v>5.18136414</v>
       </c>
-      <c r="Q91" s="17"/>
-      <c r="R91" s="17"/>
-      <c r="S91" s="17"/>
+      <c r="Q91" s="20">
+        <v>4.29391825</v>
+      </c>
+      <c r="R91" s="20">
+        <v>3.37309328</v>
+      </c>
+      <c r="S91" s="20">
+        <v>3.37309328</v>
+      </c>
       <c r="T91" s="17"/>
       <c r="U91" s="17"/>
       <c r="V91" s="11"/>
@@ -3966,16 +4142,16 @@
         <v>96</v>
       </c>
       <c r="H92" s="17">
-        <v>275.642</v>
+        <v>173.19</v>
       </c>
       <c r="I92" s="18">
         <v>277206</v>
       </c>
       <c r="J92" s="18">
-        <v>76409616.252</v>
+        <v>48009307.14</v>
       </c>
       <c r="K92" s="17">
-        <v>21.31038</v>
+        <v>13.389631</v>
       </c>
       <c r="L92" s="11"/>
       <c r="M92" s="17"/>
@@ -3986,9 +4162,15 @@
       <c r="P92" s="20">
         <v>9.23160522</v>
       </c>
-      <c r="Q92" s="17"/>
-      <c r="R92" s="17"/>
-      <c r="S92" s="17"/>
+      <c r="Q92" s="20">
+        <v>3.34740775</v>
+      </c>
+      <c r="R92" s="20">
+        <v>0.03337482</v>
+      </c>
+      <c r="S92" s="20">
+        <v>0.03337482</v>
+      </c>
       <c r="T92" s="17"/>
       <c r="U92" s="17"/>
       <c r="V92" s="11"/>
@@ -4008,16 +4190,16 @@
         <v>99</v>
       </c>
       <c r="H93" s="17">
-        <v>154.2</v>
+        <v>124.2</v>
       </c>
       <c r="I93" s="18">
         <v>26853</v>
       </c>
       <c r="J93" s="18">
-        <v>4140732.5999999996</v>
+        <v>3335142.6</v>
       </c>
       <c r="K93" s="17">
-        <v>1.154836</v>
+        <v>0.93016</v>
       </c>
       <c r="L93" s="11"/>
       <c r="M93" s="17"/>
@@ -4028,9 +4210,15 @@
       <c r="P93" s="20">
         <v>0.31005333</v>
       </c>
-      <c r="Q93" s="17"/>
-      <c r="R93" s="17"/>
-      <c r="S93" s="17"/>
+      <c r="Q93" s="20">
+        <v>0.23254</v>
+      </c>
+      <c r="R93" s="20">
+        <v>0.11627</v>
+      </c>
+      <c r="S93" s="20">
+        <v>0.11627</v>
+      </c>
       <c r="T93" s="17"/>
       <c r="U93" s="17"/>
       <c r="V93" s="11"/>
@@ -4050,16 +4238,16 @@
         <v>99</v>
       </c>
       <c r="H94" s="17">
-        <v>267.6554554</v>
+        <v>213.58</v>
       </c>
       <c r="I94" s="18">
         <v>26853</v>
       </c>
       <c r="J94" s="18">
-        <v>7187351.9438562</v>
+        <v>5735263.74</v>
       </c>
       <c r="K94" s="17">
-        <v>2.004528</v>
+        <v>1.599545</v>
       </c>
       <c r="L94" s="11"/>
       <c r="M94" s="17"/>
@@ -4070,9 +4258,15 @@
       <c r="P94" s="20">
         <v>0.39988625</v>
       </c>
-      <c r="Q94" s="17"/>
-      <c r="R94" s="17"/>
-      <c r="S94" s="17"/>
+      <c r="Q94" s="20">
+        <v>0.39988625</v>
+      </c>
+      <c r="R94" s="20">
+        <v>0.19994313</v>
+      </c>
+      <c r="S94" s="20">
+        <v>0.19994313</v>
+      </c>
       <c r="T94" s="17"/>
       <c r="U94" s="17"/>
       <c r="V94" s="11"/>
@@ -4092,16 +4286,16 @@
         <v>102</v>
       </c>
       <c r="H95" s="17">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I95" s="18">
         <v>449902</v>
       </c>
       <c r="J95" s="18">
-        <v>6298628</v>
+        <v>17546178</v>
       </c>
       <c r="K95" s="17">
-        <v>1.756666</v>
+        <v>4.893569</v>
       </c>
       <c r="L95" s="11"/>
       <c r="M95" s="17"/>
@@ -4136,16 +4330,16 @@
         <v>76</v>
       </c>
       <c r="H96" s="17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I96" s="18">
         <v>244459</v>
       </c>
       <c r="J96" s="18">
-        <v>3422426</v>
+        <v>3666885</v>
       </c>
       <c r="K96" s="17">
-        <v>0.954503</v>
+        <v>1.022682</v>
       </c>
       <c r="L96" s="11"/>
       <c r="M96" s="17"/>
@@ -4154,8 +4348,12 @@
       <c r="P96" s="17"/>
       <c r="Q96" s="17"/>
       <c r="R96" s="17"/>
-      <c r="S96" s="17"/>
-      <c r="T96" s="17"/>
+      <c r="S96" s="20">
+        <v>0.681788</v>
+      </c>
+      <c r="T96" s="20">
+        <v>0.340894</v>
+      </c>
       <c r="U96" s="17"/>
       <c r="V96" s="11"/>
       <c r="W96" s="19"/>
@@ -4174,16 +4372,16 @@
         <v>76</v>
       </c>
       <c r="H97" s="17">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I97" s="18">
         <v>668187</v>
       </c>
       <c r="J97" s="18">
-        <v>13363740</v>
+        <v>16036488</v>
       </c>
       <c r="K97" s="17">
-        <v>3.727101</v>
+        <v>4.472522</v>
       </c>
       <c r="L97" s="11"/>
       <c r="M97" s="17"/>
@@ -4192,8 +4390,12 @@
       <c r="P97" s="17"/>
       <c r="Q97" s="17"/>
       <c r="R97" s="17"/>
-      <c r="S97" s="17"/>
-      <c r="T97" s="17"/>
+      <c r="S97" s="20">
+        <v>2.98168133</v>
+      </c>
+      <c r="T97" s="20">
+        <v>1.49084067</v>
+      </c>
       <c r="U97" s="17"/>
       <c r="V97" s="11"/>
       <c r="W97" s="19"/>
@@ -4212,16 +4414,16 @@
         <v>76</v>
       </c>
       <c r="H98" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I98" s="18">
         <v>63699</v>
       </c>
       <c r="J98" s="18">
-        <v>382194</v>
+        <v>254796</v>
       </c>
       <c r="K98" s="17">
-        <v>0.106593</v>
+        <v>0.071062</v>
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="17"/>
@@ -4230,8 +4432,12 @@
       <c r="P98" s="17"/>
       <c r="Q98" s="17"/>
       <c r="R98" s="17"/>
-      <c r="S98" s="17"/>
-      <c r="T98" s="17"/>
+      <c r="S98" s="20">
+        <v>0.04737467</v>
+      </c>
+      <c r="T98" s="20">
+        <v>0.02368733</v>
+      </c>
       <c r="U98" s="17"/>
       <c r="V98" s="11"/>
       <c r="W98" s="19"/>
@@ -4250,16 +4456,16 @@
         <v>76</v>
       </c>
       <c r="H99" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" s="18">
         <v>46759</v>
       </c>
       <c r="J99" s="18">
-        <v>46759</v>
+        <v>93518</v>
       </c>
       <c r="K99" s="17">
-        <v>0.013041</v>
+        <v>0.026082</v>
       </c>
       <c r="L99" s="11"/>
       <c r="M99" s="17"/>
@@ -4268,8 +4474,12 @@
       <c r="P99" s="17"/>
       <c r="Q99" s="17"/>
       <c r="R99" s="17"/>
-      <c r="S99" s="17"/>
-      <c r="T99" s="17"/>
+      <c r="S99" s="20">
+        <v>0.017388</v>
+      </c>
+      <c r="T99" s="20">
+        <v>0.008694</v>
+      </c>
       <c r="U99" s="17"/>
       <c r="V99" s="11"/>
       <c r="W99" s="19"/>
@@ -4423,43 +4633,34 @@
       <c r="H106" s="33"/>
       <c r="I106" s="33"/>
       <c r="J106" s="33"/>
-      <c r="K106" s="34"/>
+      <c r="K106" s="33"/>
       <c r="L106" s="28"/>
-      <c r="M106" s="35">
-        <f>SUBTOTAL(9,M25:M99)</f>
-        <v>0</v>
-      </c>
-      <c r="N106" s="35">
-        <f>SUBTOTAL(9,N25:N99)</f>
-        <v>0</v>
-      </c>
-      <c r="O106" s="35">
-        <f>SUBTOTAL(9,O25:O99)</f>
-        <v>0</v>
-      </c>
-      <c r="P106" s="35">
-        <f>SUBTOTAL(9,P25:P99)</f>
-        <v>0</v>
-      </c>
-      <c r="Q106" s="35">
-        <f>SUBTOTAL(9,Q25:Q99)</f>
-        <v>0</v>
-      </c>
-      <c r="R106" s="35">
-        <f>SUBTOTAL(9,R25:R99)</f>
-        <v>0</v>
-      </c>
-      <c r="S106" s="35">
-        <f>SUBTOTAL(9,S25:S99)</f>
-        <v>0</v>
-      </c>
-      <c r="T106" s="35">
-        <f>SUBTOTAL(9,T25:T99)</f>
-        <v>0</v>
-      </c>
-      <c r="U106" s="35">
-        <f>SUBTOTAL(9,U25:U99)</f>
-        <v>0</v>
+      <c r="M106" s="34">
+        <v>2.312</v>
+      </c>
+      <c r="N106" s="34">
+        <v>6.631</v>
+      </c>
+      <c r="O106" s="34">
+        <v>16.479</v>
+      </c>
+      <c r="P106" s="34">
+        <v>29.603</v>
+      </c>
+      <c r="Q106" s="34">
+        <v>17.791</v>
+      </c>
+      <c r="R106" s="34">
+        <v>10.91</v>
+      </c>
+      <c r="S106" s="34">
+        <v>10.811</v>
+      </c>
+      <c r="T106" s="34">
+        <v>4.274</v>
+      </c>
+      <c r="U106" s="34">
+        <v>1.19</v>
       </c>
       <c r="V106" s="28"/>
       <c r="W106" s="29"/>
@@ -4468,51 +4669,42 @@
       <c r="B107" s="31"/>
       <c r="C107" s="31"/>
       <c r="D107" s="31"/>
-      <c r="E107" s="36" t="s">
+      <c r="E107" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="F107" s="30"/>
-      <c r="G107" s="30"/>
-      <c r="H107" s="30"/>
-      <c r="I107" s="30"/>
-      <c r="J107" s="30"/>
-      <c r="K107" s="37"/>
+      <c r="F107" s="33"/>
+      <c r="G107" s="33"/>
+      <c r="H107" s="33"/>
+      <c r="I107" s="33"/>
+      <c r="J107" s="33"/>
+      <c r="K107" s="33"/>
       <c r="L107" s="28"/>
-      <c r="M107" s="35">
-        <f>M106</f>
-        <v>0</v>
-      </c>
-      <c r="N107" s="35">
-        <f>M107+N106</f>
-        <v>0</v>
-      </c>
-      <c r="O107" s="35">
-        <f>N107+O106</f>
-        <v>0</v>
-      </c>
-      <c r="P107" s="35">
-        <f>O107+P106</f>
-        <v>0</v>
-      </c>
-      <c r="Q107" s="35">
-        <f>P107+Q106</f>
-        <v>0</v>
-      </c>
-      <c r="R107" s="35">
-        <f>Q107+R106</f>
-        <v>0</v>
-      </c>
-      <c r="S107" s="35">
-        <f>R107+S106</f>
-        <v>0</v>
-      </c>
-      <c r="T107" s="35">
-        <f>S107+T106</f>
-        <v>0</v>
-      </c>
-      <c r="U107" s="35">
-        <f>T107+U106</f>
-        <v>0</v>
+      <c r="M107" s="34">
+        <v>2.312</v>
+      </c>
+      <c r="N107" s="34">
+        <v>8.943</v>
+      </c>
+      <c r="O107" s="34">
+        <v>25.422</v>
+      </c>
+      <c r="P107" s="34">
+        <v>55.025</v>
+      </c>
+      <c r="Q107" s="34">
+        <v>72.816</v>
+      </c>
+      <c r="R107" s="34">
+        <v>83.726</v>
+      </c>
+      <c r="S107" s="34">
+        <v>94.537</v>
+      </c>
+      <c r="T107" s="34">
+        <v>98.81</v>
+      </c>
+      <c r="U107" s="34">
+        <v>100</v>
       </c>
       <c r="V107" s="28"/>
       <c r="W107" s="29"/>
@@ -4523,7 +4715,7 @@
       </c>
       <c r="C108" s="31"/>
       <c r="D108" s="31"/>
-      <c r="E108" s="38" t="s">
+      <c r="E108" s="35" t="s">
         <v>126</v>
       </c>
       <c r="F108" s="33"/>
@@ -4531,17 +4723,35 @@
       <c r="H108" s="33"/>
       <c r="I108" s="33"/>
       <c r="J108" s="33"/>
-      <c r="K108" s="34"/>
+      <c r="K108" s="33"/>
       <c r="L108" s="28"/>
-      <c r="M108" s="35"/>
-      <c r="N108" s="35"/>
-      <c r="O108" s="35"/>
-      <c r="P108" s="35"/>
-      <c r="Q108" s="35"/>
-      <c r="R108" s="35"/>
-      <c r="S108" s="35"/>
-      <c r="T108" s="35"/>
-      <c r="U108" s="35"/>
+      <c r="M108" s="34">
+        <v>0</v>
+      </c>
+      <c r="N108" s="34">
+        <v>0</v>
+      </c>
+      <c r="O108" s="34">
+        <v>0</v>
+      </c>
+      <c r="P108" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="34">
+        <v>0</v>
+      </c>
+      <c r="R108" s="34">
+        <v>0</v>
+      </c>
+      <c r="S108" s="34">
+        <v>0</v>
+      </c>
+      <c r="T108" s="34">
+        <v>0</v>
+      </c>
+      <c r="U108" s="34">
+        <v>0</v>
+      </c>
       <c r="V108" s="28"/>
       <c r="W108" s="29"/>
     </row>
@@ -4549,157 +4759,193 @@
       <c r="B109" s="31"/>
       <c r="C109" s="31"/>
       <c r="D109" s="31"/>
-      <c r="E109" s="39" t="s">
+      <c r="E109" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="F109" s="30"/>
-      <c r="G109" s="30"/>
-      <c r="H109" s="30"/>
-      <c r="I109" s="30"/>
-      <c r="J109" s="30"/>
-      <c r="K109" s="37"/>
+      <c r="F109" s="33"/>
+      <c r="G109" s="33"/>
+      <c r="H109" s="33"/>
+      <c r="I109" s="33"/>
+      <c r="J109" s="33"/>
+      <c r="K109" s="33"/>
       <c r="L109" s="28"/>
-      <c r="M109" s="35"/>
-      <c r="N109" s="35"/>
-      <c r="O109" s="35"/>
-      <c r="P109" s="35"/>
-      <c r="Q109" s="35"/>
-      <c r="R109" s="35"/>
-      <c r="S109" s="35"/>
-      <c r="T109" s="35"/>
-      <c r="U109" s="35"/>
+      <c r="M109" s="34">
+        <v>0</v>
+      </c>
+      <c r="N109" s="34">
+        <v>0</v>
+      </c>
+      <c r="O109" s="34">
+        <v>0</v>
+      </c>
+      <c r="P109" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="34">
+        <v>0</v>
+      </c>
+      <c r="R109" s="34">
+        <v>0</v>
+      </c>
+      <c r="S109" s="34">
+        <v>0</v>
+      </c>
+      <c r="T109" s="34">
+        <v>0</v>
+      </c>
+      <c r="U109" s="34">
+        <v>0</v>
+      </c>
       <c r="V109" s="28"/>
       <c r="W109" s="29"/>
     </row>
     <row r="110" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B110" s="40" t="s">
+      <c r="B110" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="C110" s="40"/>
-      <c r="D110" s="40"/>
-      <c r="E110" s="41" t="s">
+      <c r="C110" s="36"/>
+      <c r="D110" s="36"/>
+      <c r="E110" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="F110" s="42"/>
-      <c r="G110" s="42"/>
-      <c r="H110" s="42"/>
-      <c r="I110" s="42"/>
-      <c r="J110" s="42"/>
-      <c r="K110" s="43"/>
-      <c r="L110" s="44"/>
-      <c r="M110" s="35"/>
-      <c r="N110" s="35"/>
-      <c r="O110" s="35"/>
-      <c r="P110" s="35"/>
-      <c r="Q110" s="35"/>
-      <c r="R110" s="35"/>
-      <c r="S110" s="35"/>
-      <c r="T110" s="35"/>
-      <c r="U110" s="35"/>
-      <c r="V110" s="44"/>
-      <c r="W110" s="45"/>
+      <c r="F110" s="33"/>
+      <c r="G110" s="33"/>
+      <c r="H110" s="33"/>
+      <c r="I110" s="33"/>
+      <c r="J110" s="33"/>
+      <c r="K110" s="33"/>
+      <c r="L110" s="37"/>
+      <c r="M110" s="34">
+        <v>-2.312</v>
+      </c>
+      <c r="N110" s="34">
+        <v>-8.943</v>
+      </c>
+      <c r="O110" s="34">
+        <v>-25.422</v>
+      </c>
+      <c r="P110" s="34">
+        <v>-55.025</v>
+      </c>
+      <c r="Q110" s="34">
+        <v>-72.816</v>
+      </c>
+      <c r="R110" s="34">
+        <v>-83.726</v>
+      </c>
+      <c r="S110" s="34">
+        <v>-94.537</v>
+      </c>
+      <c r="T110" s="34">
+        <v>-98.81</v>
+      </c>
+      <c r="U110" s="34">
+        <v>-100</v>
+      </c>
+      <c r="V110" s="37"/>
+      <c r="W110" s="38"/>
     </row>
     <row r="111" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B111" s="46"/>
-      <c r="W111" s="47"/>
+      <c r="B111" s="39"/>
+      <c r="W111" s="40"/>
     </row>
     <row r="112" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B112" s="46"/>
-      <c r="W112" s="47"/>
+      <c r="B112" s="39"/>
+      <c r="W112" s="40"/>
     </row>
     <row r="113" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B113" s="46"/>
-      <c r="F113" s="48" t="s">
+      <c r="B113" s="39"/>
+      <c r="F113" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="M113" s="48" t="s">
+      <c r="M113" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="U113" s="48" t="s">
+      <c r="U113" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="W113" s="47"/>
+      <c r="W113" s="40"/>
     </row>
     <row r="114" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B114" s="46"/>
-      <c r="F114" s="48" t="s">
+      <c r="B114" s="39"/>
+      <c r="F114" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="M114" s="48" t="s">
+      <c r="M114" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="U114" s="48" t="s">
+      <c r="U114" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="W114" s="47"/>
+      <c r="W114" s="40"/>
     </row>
     <row r="115" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B115" s="46"/>
-      <c r="F115" s="48" t="s">
+      <c r="B115" s="39"/>
+      <c r="F115" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="M115" s="48" t="s">
+      <c r="M115" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="U115" s="48" t="s">
+      <c r="U115" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="W115" s="47"/>
+      <c r="W115" s="40"/>
     </row>
     <row r="116" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B116" s="46"/>
-      <c r="F116" s="48" t="s">
+      <c r="B116" s="39"/>
+      <c r="F116" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="U116" s="48" t="s">
+      <c r="U116" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="W116" s="47"/>
+      <c r="W116" s="40"/>
     </row>
     <row r="117" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B117" s="46"/>
-      <c r="W117" s="47"/>
+      <c r="B117" s="39"/>
+      <c r="W117" s="40"/>
     </row>
     <row r="118" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B118" s="46"/>
-      <c r="W118" s="47"/>
+      <c r="B118" s="39"/>
+      <c r="W118" s="40"/>
     </row>
     <row r="119" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B119" s="46"/>
-      <c r="W119" s="47"/>
+      <c r="B119" s="39"/>
+      <c r="W119" s="40"/>
     </row>
     <row r="120" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B120" s="46"/>
-      <c r="W120" s="47"/>
+      <c r="B120" s="39"/>
+      <c r="W120" s="40"/>
     </row>
     <row r="121" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B121" s="46"/>
-      <c r="F121" s="49" t="s">
+      <c r="B121" s="39"/>
+      <c r="F121" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="M121" s="49" t="s">
+      <c r="M121" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="U121" s="49" t="s">
+      <c r="U121" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="W121" s="47"/>
+      <c r="W121" s="40"/>
     </row>
     <row r="122" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B122" s="46"/>
-      <c r="F122" s="50" t="s">
+      <c r="B122" s="39"/>
+      <c r="F122" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="M122" s="50" t="s">
+      <c r="M122" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="U122" s="50" t="s">
+      <c r="U122" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="W122" s="47"/>
+      <c r="W122" s="40"/>
     </row>
     <row r="123" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B123" s="51"/>
+      <c r="B123" s="44"/>
       <c r="C123" s="30"/>
       <c r="D123" s="30"/>
       <c r="E123" s="30"/>
@@ -4720,7 +4966,7 @@
       <c r="T123" s="30"/>
       <c r="U123" s="30"/>
       <c r="V123" s="30"/>
-      <c r="W123" s="37"/>
+      <c r="W123" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="88">
@@ -4841,11 +5087,11 @@
       <c r="A2" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="52">
+      <c r="B2" s="46">
         <v>2.312</v>
       </c>
-      <c r="C2" s="52">
-        <v>7.252</v>
+      <c r="C2" s="46">
+        <v>0</v>
       </c>
       <c r="F2">
         <v>21</v>
@@ -4855,11 +5101,11 @@
       <c r="A3" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="52">
+      <c r="B3" s="46">
         <v>8.943</v>
       </c>
-      <c r="C3" s="52">
-        <v>10.05</v>
+      <c r="C3" s="46">
+        <v>0</v>
       </c>
       <c r="F3">
         <v>25</v>
@@ -4869,80 +5115,83 @@
       <c r="A4" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="52">
+      <c r="B4" s="46">
         <v>25.422</v>
       </c>
-      <c r="C4" s="52">
-        <v>28.684</v>
+      <c r="C4" s="46">
+        <v>0</v>
       </c>
       <c r="F4">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="52">
+      <c r="B5" s="46">
         <v>55.025</v>
       </c>
-      <c r="C5" s="52">
-        <v>77.035</v>
+      <c r="C5" s="46">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="52">
-        <v>55.025</v>
-      </c>
-      <c r="C6" s="52">
-        <v>73.061</v>
+      <c r="B6" s="46">
+        <v>72.816</v>
+      </c>
+      <c r="C6" s="46">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="52">
-        <v>55.025</v>
-      </c>
-      <c r="C7" s="52">
-        <v>73.061</v>
+      <c r="B7" s="46">
+        <v>83.726</v>
+      </c>
+      <c r="C7" s="46">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="52">
-        <v>55.025</v>
-      </c>
-      <c r="C8" s="52">
-        <v>73.061</v>
+      <c r="B8" s="46">
+        <v>94.537</v>
+      </c>
+      <c r="C8" s="46">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="52">
-        <v>55.025</v>
-      </c>
-      <c r="C9" s="52">
-        <v>73.061</v>
+      <c r="B9" s="46">
+        <v>98.81</v>
+      </c>
+      <c r="C9" s="46">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="52">
-        <v>55.025</v>
-      </c>
-      <c r="C10" s="52">
-        <v>73.061</v>
+      <c r="B10" s="46">
+        <v>100</v>
+      </c>
+      <c r="C10" s="46">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/backend/temp_schedule.xlsx
+++ b/backend/temp_schedule.xlsx
@@ -1693,31 +1693,31 @@
       </c>
       <c r="L29" s="11"/>
       <c r="M29" s="20">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="N29" s="20">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="O29" s="20">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="P29" s="20">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="Q29" s="20">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="R29" s="20">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="S29" s="20">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="T29" s="20">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="U29" s="20">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="V29" s="11"/>
       <c r="W29" s="19"/>
@@ -1801,31 +1801,31 @@
       </c>
       <c r="L32" s="11"/>
       <c r="M32" s="20">
-        <v>0.00929656</v>
+        <v>0.0093</v>
       </c>
       <c r="N32" s="20">
-        <v>0.00929656</v>
+        <v>0.0093</v>
       </c>
       <c r="O32" s="20">
-        <v>0.00929656</v>
+        <v>0.0093</v>
       </c>
       <c r="P32" s="20">
-        <v>0.00929656</v>
+        <v>0.0093</v>
       </c>
       <c r="Q32" s="20">
-        <v>0.00929656</v>
+        <v>0.0093</v>
       </c>
       <c r="R32" s="20">
-        <v>0.00929656</v>
+        <v>0.0093</v>
       </c>
       <c r="S32" s="20">
-        <v>0.00929656</v>
+        <v>0.0093</v>
       </c>
       <c r="T32" s="20">
-        <v>0.00929656</v>
+        <v>0.0093</v>
       </c>
       <c r="U32" s="20">
-        <v>0.00929656</v>
+        <v>0.0093</v>
       </c>
       <c r="V32" s="11"/>
       <c r="W32" s="19"/>
@@ -1857,31 +1857,31 @@
       </c>
       <c r="L33" s="11"/>
       <c r="M33" s="20">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="N33" s="20">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="O33" s="20">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="P33" s="20">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="Q33" s="20">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="R33" s="20">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="S33" s="20">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="T33" s="20">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="U33" s="20">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="V33" s="11"/>
       <c r="W33" s="19"/>
@@ -1965,31 +1965,31 @@
       </c>
       <c r="L36" s="11"/>
       <c r="M36" s="20">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="N36" s="20">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="O36" s="20">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="P36" s="20">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="Q36" s="20">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="R36" s="20">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="S36" s="20">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="T36" s="20">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="U36" s="20">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="V36" s="11"/>
       <c r="W36" s="19"/>
@@ -2021,31 +2021,31 @@
       </c>
       <c r="L37" s="11"/>
       <c r="M37" s="20">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="N37" s="20">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="O37" s="20">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="P37" s="20">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="Q37" s="20">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="R37" s="20">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="S37" s="20">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="T37" s="20">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="U37" s="20">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="V37" s="11"/>
       <c r="W37" s="19"/>
@@ -2077,31 +2077,31 @@
       </c>
       <c r="L38" s="11"/>
       <c r="M38" s="20">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="N38" s="20">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="O38" s="20">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="P38" s="20">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="Q38" s="20">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="R38" s="20">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="S38" s="20">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="T38" s="20">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="U38" s="20">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="V38" s="11"/>
       <c r="W38" s="19"/>
@@ -2133,31 +2133,31 @@
       </c>
       <c r="L39" s="11"/>
       <c r="M39" s="20">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="N39" s="20">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="O39" s="20">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="P39" s="20">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="Q39" s="20">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="R39" s="20">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="S39" s="20">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="T39" s="20">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="U39" s="20">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="V39" s="11"/>
       <c r="W39" s="19"/>
@@ -2241,31 +2241,31 @@
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="20">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="N42" s="20">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="O42" s="20">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="P42" s="20">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="Q42" s="20">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="R42" s="20">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="S42" s="20">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="T42" s="20">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="U42" s="20">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="V42" s="11"/>
       <c r="W42" s="19"/>
@@ -2349,31 +2349,31 @@
       </c>
       <c r="L45" s="11"/>
       <c r="M45" s="20">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="N45" s="20">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="O45" s="20">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="P45" s="20">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="Q45" s="20">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="R45" s="20">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="S45" s="20">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="T45" s="20">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="U45" s="20">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="V45" s="11"/>
       <c r="W45" s="19"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="L48" s="11"/>
       <c r="M48" s="20">
-        <v>0.023706</v>
+        <v>0.0237</v>
       </c>
       <c r="N48" s="17"/>
       <c r="O48" s="17"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L49" s="11"/>
       <c r="M49" s="20">
-        <v>0.023706</v>
+        <v>0.0237</v>
       </c>
       <c r="N49" s="17"/>
       <c r="O49" s="17"/>
@@ -2589,10 +2589,10 @@
       </c>
       <c r="L52" s="11"/>
       <c r="M52" s="20">
-        <v>0.159058</v>
+        <v>0.1591</v>
       </c>
       <c r="N52" s="20">
-        <v>0.159058</v>
+        <v>0.1591</v>
       </c>
       <c r="O52" s="17"/>
       <c r="P52" s="17"/>
@@ -2627,22 +2627,22 @@
         <v>52997594.52</v>
       </c>
       <c r="K53" s="17">
-        <v>14.780848</v>
+        <v>14.780847</v>
       </c>
       <c r="L53" s="11"/>
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
       <c r="O53" s="20">
-        <v>3.695212</v>
+        <v>3.6952</v>
       </c>
       <c r="P53" s="20">
-        <v>3.695212</v>
+        <v>3.6952</v>
       </c>
       <c r="Q53" s="20">
-        <v>3.695212</v>
+        <v>3.6952</v>
       </c>
       <c r="R53" s="20">
-        <v>3.695212</v>
+        <v>3.6952</v>
       </c>
       <c r="S53" s="17"/>
       <c r="T53" s="17"/>
@@ -2679,16 +2679,16 @@
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
       <c r="O54" s="20">
-        <v>0.18715525</v>
+        <v>0.1872</v>
       </c>
       <c r="P54" s="20">
-        <v>0.18715525</v>
+        <v>0.1872</v>
       </c>
       <c r="Q54" s="20">
-        <v>0.18715525</v>
+        <v>0.1872</v>
       </c>
       <c r="R54" s="20">
-        <v>0.18715525</v>
+        <v>0.1872</v>
       </c>
       <c r="S54" s="17"/>
       <c r="T54" s="17"/>
@@ -2724,16 +2724,16 @@
       <c r="L55" s="11"/>
       <c r="M55" s="17"/>
       <c r="N55" s="20">
-        <v>0.652855</v>
+        <v>0.6529</v>
       </c>
       <c r="O55" s="20">
-        <v>0.652855</v>
+        <v>0.6529</v>
       </c>
       <c r="P55" s="20">
-        <v>0.652855</v>
+        <v>0.6529</v>
       </c>
       <c r="Q55" s="20">
-        <v>0.652855</v>
+        <v>0.6529</v>
       </c>
       <c r="R55" s="17"/>
       <c r="S55" s="17"/>
@@ -2765,14 +2765,14 @@
         <v>5398824</v>
       </c>
       <c r="K56" s="17">
-        <v>1.505714</v>
+        <v>1.505713</v>
       </c>
       <c r="L56" s="11"/>
       <c r="M56" s="20">
-        <v>0.752857</v>
+        <v>0.7529</v>
       </c>
       <c r="N56" s="20">
-        <v>0.752857</v>
+        <v>0.7529</v>
       </c>
       <c r="O56" s="17"/>
       <c r="P56" s="17"/>
@@ -2815,16 +2815,16 @@
       <c r="O57" s="17"/>
       <c r="P57" s="17"/>
       <c r="Q57" s="20">
-        <v>0.55906525</v>
+        <v>0.5591</v>
       </c>
       <c r="R57" s="20">
-        <v>0.55906525</v>
+        <v>0.5591</v>
       </c>
       <c r="S57" s="20">
-        <v>0.55906525</v>
+        <v>0.5591</v>
       </c>
       <c r="T57" s="20">
-        <v>0.55906525</v>
+        <v>0.5591</v>
       </c>
       <c r="U57" s="17"/>
       <c r="V57" s="11"/>
@@ -2861,16 +2861,16 @@
       <c r="O58" s="17"/>
       <c r="P58" s="17"/>
       <c r="Q58" s="20">
-        <v>0.013324</v>
+        <v>0.0133</v>
       </c>
       <c r="R58" s="20">
-        <v>0.013324</v>
+        <v>0.0133</v>
       </c>
       <c r="S58" s="20">
-        <v>0.013324</v>
+        <v>0.0133</v>
       </c>
       <c r="T58" s="20">
-        <v>0.013324</v>
+        <v>0.0133</v>
       </c>
       <c r="U58" s="17"/>
       <c r="V58" s="11"/>
@@ -2955,10 +2955,10 @@
       </c>
       <c r="L61" s="11"/>
       <c r="M61" s="20">
-        <v>0.110314</v>
+        <v>0.1103</v>
       </c>
       <c r="N61" s="20">
-        <v>0.110314</v>
+        <v>0.1103</v>
       </c>
       <c r="O61" s="17"/>
       <c r="P61" s="17"/>
@@ -2999,16 +2999,16 @@
       <c r="M62" s="17"/>
       <c r="N62" s="17"/>
       <c r="O62" s="20">
-        <v>1.70853283</v>
+        <v>1.7085</v>
       </c>
       <c r="P62" s="20">
-        <v>3.41706567</v>
+        <v>3.4171</v>
       </c>
       <c r="Q62" s="20">
-        <v>3.41706567</v>
+        <v>3.4171</v>
       </c>
       <c r="R62" s="20">
-        <v>1.70853283</v>
+        <v>1.7085</v>
       </c>
       <c r="S62" s="17"/>
       <c r="T62" s="17"/>
@@ -3045,16 +3045,16 @@
       <c r="M63" s="17"/>
       <c r="N63" s="17"/>
       <c r="O63" s="20">
-        <v>0.12746625</v>
+        <v>0.1275</v>
       </c>
       <c r="P63" s="20">
-        <v>0.12746625</v>
+        <v>0.1275</v>
       </c>
       <c r="Q63" s="20">
-        <v>0.12746625</v>
+        <v>0.1275</v>
       </c>
       <c r="R63" s="20">
-        <v>0.12746625</v>
+        <v>0.1275</v>
       </c>
       <c r="S63" s="17"/>
       <c r="T63" s="17"/>
@@ -3090,16 +3090,16 @@
       <c r="L64" s="11"/>
       <c r="M64" s="17"/>
       <c r="N64" s="20">
-        <v>0.5159792</v>
+        <v>0.516</v>
       </c>
       <c r="O64" s="20">
-        <v>0.5159792</v>
+        <v>0.516</v>
       </c>
       <c r="P64" s="20">
-        <v>0.5159792</v>
+        <v>0.516</v>
       </c>
       <c r="Q64" s="20">
-        <v>0.1300014</v>
+        <v>0.13</v>
       </c>
       <c r="R64" s="17"/>
       <c r="S64" s="17"/>
@@ -3135,10 +3135,10 @@
       </c>
       <c r="L65" s="11"/>
       <c r="M65" s="20">
-        <v>0.55015167</v>
+        <v>0.5502</v>
       </c>
       <c r="N65" s="20">
-        <v>0.45365733</v>
+        <v>0.4537</v>
       </c>
       <c r="O65" s="17"/>
       <c r="P65" s="17"/>
@@ -3173,7 +3173,7 @@
         <v>5345496</v>
       </c>
       <c r="K66" s="17">
-        <v>1.490841</v>
+        <v>1.49084</v>
       </c>
       <c r="L66" s="11"/>
       <c r="M66" s="17"/>
@@ -3181,16 +3181,16 @@
       <c r="O66" s="17"/>
       <c r="P66" s="17"/>
       <c r="Q66" s="20">
-        <v>0.37271025</v>
+        <v>0.3727</v>
       </c>
       <c r="R66" s="20">
-        <v>0.37271025</v>
+        <v>0.3727</v>
       </c>
       <c r="S66" s="20">
-        <v>0.37271025</v>
+        <v>0.3727</v>
       </c>
       <c r="T66" s="20">
-        <v>0.37271025</v>
+        <v>0.3727</v>
       </c>
       <c r="U66" s="17"/>
       <c r="V66" s="11"/>
@@ -3227,16 +3227,16 @@
       <c r="O67" s="17"/>
       <c r="P67" s="17"/>
       <c r="Q67" s="20">
-        <v>0.00888275</v>
+        <v>0.0089</v>
       </c>
       <c r="R67" s="20">
-        <v>0.00888275</v>
+        <v>0.0089</v>
       </c>
       <c r="S67" s="20">
-        <v>0.00888275</v>
+        <v>0.0089</v>
       </c>
       <c r="T67" s="20">
-        <v>0.00888275</v>
+        <v>0.0089</v>
       </c>
       <c r="U67" s="17"/>
       <c r="V67" s="11"/>
@@ -3396,10 +3396,10 @@
       <c r="R72" s="17"/>
       <c r="S72" s="17"/>
       <c r="T72" s="20">
-        <v>0.238524</v>
+        <v>0.2385</v>
       </c>
       <c r="U72" s="20">
-        <v>0.119262</v>
+        <v>0.1193</v>
       </c>
       <c r="V72" s="11"/>
       <c r="W72" s="19"/>
@@ -3438,10 +3438,10 @@
       <c r="R73" s="17"/>
       <c r="S73" s="17"/>
       <c r="T73" s="20">
-        <v>0.06340867</v>
+        <v>0.0634</v>
       </c>
       <c r="U73" s="20">
-        <v>0.03170433</v>
+        <v>0.0317</v>
       </c>
       <c r="V73" s="11"/>
       <c r="W73" s="19"/>
@@ -3480,10 +3480,10 @@
       <c r="R74" s="17"/>
       <c r="S74" s="17"/>
       <c r="T74" s="20">
-        <v>0.022808</v>
+        <v>0.0228</v>
       </c>
       <c r="U74" s="20">
-        <v>0.011404</v>
+        <v>0.0114</v>
       </c>
       <c r="V74" s="11"/>
       <c r="W74" s="19"/>
@@ -3522,10 +3522,10 @@
       <c r="R75" s="17"/>
       <c r="S75" s="17"/>
       <c r="T75" s="20">
-        <v>0.16730133</v>
+        <v>0.1673</v>
       </c>
       <c r="U75" s="20">
-        <v>0.08365067</v>
+        <v>0.0837</v>
       </c>
       <c r="V75" s="11"/>
       <c r="W75" s="19"/>
@@ -3564,10 +3564,10 @@
       <c r="R76" s="17"/>
       <c r="S76" s="17"/>
       <c r="T76" s="20">
-        <v>0.02368733</v>
+        <v>0.0237</v>
       </c>
       <c r="U76" s="20">
-        <v>0.01184367</v>
+        <v>0.0118</v>
       </c>
       <c r="V76" s="11"/>
       <c r="W76" s="19"/>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L79" s="11"/>
       <c r="M79" s="20">
-        <v>0.315455</v>
+        <v>0.3155</v>
       </c>
       <c r="N79" s="17"/>
       <c r="O79" s="17"/>
@@ -3678,20 +3678,20 @@
         <v>96</v>
       </c>
       <c r="H80" s="17">
-        <v>135.74925</v>
+        <v>135.7493</v>
       </c>
       <c r="I80" s="18">
         <v>5500</v>
       </c>
       <c r="J80" s="18">
-        <v>746620.8749999999</v>
+        <v>746621.15</v>
       </c>
       <c r="K80" s="17">
         <v>0.20823</v>
       </c>
       <c r="L80" s="11"/>
       <c r="M80" s="20">
-        <v>0.20823</v>
+        <v>0.2082</v>
       </c>
       <c r="N80" s="17"/>
       <c r="O80" s="17"/>
@@ -3718,27 +3718,27 @@
         <v>96</v>
       </c>
       <c r="H81" s="17">
-        <v>135.74925</v>
+        <v>135.7493</v>
       </c>
       <c r="I81" s="18">
         <v>255550</v>
       </c>
       <c r="J81" s="18">
-        <v>34690720.8375</v>
+        <v>34690733.615</v>
       </c>
       <c r="K81" s="17">
-        <v>9.675123</v>
+        <v>9.675126</v>
       </c>
       <c r="L81" s="11"/>
       <c r="M81" s="17"/>
       <c r="N81" s="20">
-        <v>1.20939038</v>
+        <v>1.2094</v>
       </c>
       <c r="O81" s="20">
-        <v>4.78931444</v>
+        <v>4.7893</v>
       </c>
       <c r="P81" s="20">
-        <v>3.67641818</v>
+        <v>3.6764</v>
       </c>
       <c r="Q81" s="17"/>
       <c r="R81" s="17"/>
@@ -3776,10 +3776,10 @@
       <c r="L82" s="11"/>
       <c r="M82" s="17"/>
       <c r="N82" s="20">
-        <v>0.2472935</v>
+        <v>0.2473</v>
       </c>
       <c r="O82" s="20">
-        <v>0.2472935</v>
+        <v>0.2473</v>
       </c>
       <c r="P82" s="17"/>
       <c r="Q82" s="17"/>
@@ -3821,13 +3821,13 @@
       <c r="O83" s="17"/>
       <c r="P83" s="17"/>
       <c r="Q83" s="20">
-        <v>0.1845066</v>
+        <v>0.1845</v>
       </c>
       <c r="R83" s="20">
-        <v>0.34594988</v>
+        <v>0.3459</v>
       </c>
       <c r="S83" s="20">
-        <v>2.23714252</v>
+        <v>2.2371</v>
       </c>
       <c r="T83" s="17"/>
       <c r="U83" s="17"/>
@@ -3862,10 +3862,10 @@
       <c r="L84" s="11"/>
       <c r="M84" s="17"/>
       <c r="N84" s="20">
-        <v>0.5019045</v>
+        <v>0.5019</v>
       </c>
       <c r="O84" s="20">
-        <v>0.5019045</v>
+        <v>0.5019</v>
       </c>
       <c r="P84" s="17"/>
       <c r="Q84" s="17"/>
@@ -3899,7 +3899,7 @@
         <v>5345496</v>
       </c>
       <c r="K85" s="17">
-        <v>1.490841</v>
+        <v>1.49084</v>
       </c>
       <c r="L85" s="11"/>
       <c r="M85" s="17"/>
@@ -3910,10 +3910,10 @@
       <c r="R85" s="17"/>
       <c r="S85" s="17"/>
       <c r="T85" s="20">
-        <v>0.7454205</v>
+        <v>0.7454</v>
       </c>
       <c r="U85" s="20">
-        <v>0.7454205</v>
+        <v>0.7454</v>
       </c>
       <c r="V85" s="11"/>
       <c r="W85" s="19"/>
@@ -3952,10 +3952,10 @@
       <c r="R86" s="17"/>
       <c r="S86" s="17"/>
       <c r="T86" s="20">
-        <v>0.0177655</v>
+        <v>0.0178</v>
       </c>
       <c r="U86" s="20">
-        <v>0.0177655</v>
+        <v>0.017</v>
       </c>
       <c r="V86" s="11"/>
       <c r="W86" s="19"/>
@@ -4068,7 +4068,7 @@
       <c r="L90" s="11"/>
       <c r="M90" s="17"/>
       <c r="N90" s="20">
-        <v>0.63532</v>
+        <v>0.6353</v>
       </c>
       <c r="O90" s="17"/>
       <c r="P90" s="17"/>
@@ -4103,25 +4103,25 @@
         <v>61584381.18</v>
       </c>
       <c r="K91" s="17">
-        <v>17.175673</v>
+        <v>17.175672</v>
       </c>
       <c r="L91" s="11"/>
       <c r="M91" s="17"/>
       <c r="N91" s="17"/>
       <c r="O91" s="20">
-        <v>0.95420406</v>
+        <v>0.9542</v>
       </c>
       <c r="P91" s="20">
-        <v>5.18136414</v>
+        <v>5.1814</v>
       </c>
       <c r="Q91" s="20">
-        <v>4.29391825</v>
+        <v>4.2939</v>
       </c>
       <c r="R91" s="20">
-        <v>3.37309328</v>
+        <v>3.3731</v>
       </c>
       <c r="S91" s="20">
-        <v>3.37309328</v>
+        <v>3.3731</v>
       </c>
       <c r="T91" s="17"/>
       <c r="U91" s="17"/>
@@ -4157,19 +4157,19 @@
       <c r="M92" s="17"/>
       <c r="N92" s="17"/>
       <c r="O92" s="20">
-        <v>0.74386839</v>
+        <v>0.7439</v>
       </c>
       <c r="P92" s="20">
-        <v>9.23160522</v>
+        <v>9.2316</v>
       </c>
       <c r="Q92" s="20">
-        <v>3.34740775</v>
+        <v>3.3474</v>
       </c>
       <c r="R92" s="20">
-        <v>0.03337482</v>
+        <v>0.0334</v>
       </c>
       <c r="S92" s="20">
-        <v>0.03337482</v>
+        <v>0.0334</v>
       </c>
       <c r="T92" s="17"/>
       <c r="U92" s="17"/>
@@ -4205,19 +4205,19 @@
       <c r="M93" s="17"/>
       <c r="N93" s="17"/>
       <c r="O93" s="20">
-        <v>0.15502667</v>
+        <v>0.155</v>
       </c>
       <c r="P93" s="20">
-        <v>0.31005333</v>
+        <v>0.3101</v>
       </c>
       <c r="Q93" s="20">
-        <v>0.23254</v>
+        <v>0.2325</v>
       </c>
       <c r="R93" s="20">
-        <v>0.11627</v>
+        <v>0.1163</v>
       </c>
       <c r="S93" s="20">
-        <v>0.11627</v>
+        <v>0.1163</v>
       </c>
       <c r="T93" s="17"/>
       <c r="U93" s="17"/>
@@ -4253,19 +4253,19 @@
       <c r="M94" s="17"/>
       <c r="N94" s="17"/>
       <c r="O94" s="20">
-        <v>0.39988625</v>
+        <v>0.3999</v>
       </c>
       <c r="P94" s="20">
-        <v>0.39988625</v>
+        <v>0.3999</v>
       </c>
       <c r="Q94" s="20">
-        <v>0.39988625</v>
+        <v>0.3999</v>
       </c>
       <c r="R94" s="20">
-        <v>0.19994313</v>
+        <v>0.1999</v>
       </c>
       <c r="S94" s="20">
-        <v>0.19994313</v>
+        <v>0.1999</v>
       </c>
       <c r="T94" s="17"/>
       <c r="U94" s="17"/>
@@ -4300,13 +4300,13 @@
       <c r="L95" s="11"/>
       <c r="M95" s="17"/>
       <c r="N95" s="20">
-        <v>1.22339225</v>
+        <v>1.2234</v>
       </c>
       <c r="O95" s="20">
-        <v>1.63118967</v>
+        <v>1.6312</v>
       </c>
       <c r="P95" s="20">
-        <v>2.03898708</v>
+        <v>2.039</v>
       </c>
       <c r="Q95" s="17"/>
       <c r="R95" s="17"/>
@@ -4349,10 +4349,10 @@
       <c r="Q96" s="17"/>
       <c r="R96" s="17"/>
       <c r="S96" s="20">
-        <v>0.681788</v>
+        <v>0.6818</v>
       </c>
       <c r="T96" s="20">
-        <v>0.340894</v>
+        <v>0.3409</v>
       </c>
       <c r="U96" s="17"/>
       <c r="V96" s="11"/>
@@ -4381,7 +4381,7 @@
         <v>16036488</v>
       </c>
       <c r="K97" s="17">
-        <v>4.472522</v>
+        <v>4.472521</v>
       </c>
       <c r="L97" s="11"/>
       <c r="M97" s="17"/>
@@ -4391,10 +4391,10 @@
       <c r="Q97" s="17"/>
       <c r="R97" s="17"/>
       <c r="S97" s="20">
-        <v>2.98168133</v>
+        <v>2.9817</v>
       </c>
       <c r="T97" s="20">
-        <v>1.49084067</v>
+        <v>1.4908</v>
       </c>
       <c r="U97" s="17"/>
       <c r="V97" s="11"/>
@@ -4433,10 +4433,10 @@
       <c r="Q98" s="17"/>
       <c r="R98" s="17"/>
       <c r="S98" s="20">
-        <v>0.04737467</v>
+        <v>0.0474</v>
       </c>
       <c r="T98" s="20">
-        <v>0.02368733</v>
+        <v>0.0237</v>
       </c>
       <c r="U98" s="17"/>
       <c r="V98" s="11"/>
@@ -4475,10 +4475,10 @@
       <c r="Q99" s="17"/>
       <c r="R99" s="17"/>
       <c r="S99" s="20">
-        <v>0.017388</v>
+        <v>0.017</v>
       </c>
       <c r="T99" s="20">
-        <v>0.008694</v>
+        <v>0.0087</v>
       </c>
       <c r="U99" s="17"/>
       <c r="V99" s="11"/>
@@ -4636,7 +4636,7 @@
       <c r="K106" s="33"/>
       <c r="L106" s="28"/>
       <c r="M106" s="34">
-        <v>2.312</v>
+        <v>2.313</v>
       </c>
       <c r="N106" s="34">
         <v>6.631</v>
@@ -4660,7 +4660,7 @@
         <v>4.274</v>
       </c>
       <c r="U106" s="34">
-        <v>1.19</v>
+        <v>1.189</v>
       </c>
       <c r="V106" s="28"/>
       <c r="W106" s="29"/>
@@ -4680,28 +4680,28 @@
       <c r="K107" s="33"/>
       <c r="L107" s="28"/>
       <c r="M107" s="34">
-        <v>2.312</v>
+        <v>2.313</v>
       </c>
       <c r="N107" s="34">
-        <v>8.943</v>
+        <v>8.944</v>
       </c>
       <c r="O107" s="34">
         <v>25.422</v>
       </c>
       <c r="P107" s="34">
-        <v>55.025</v>
+        <v>55.026</v>
       </c>
       <c r="Q107" s="34">
-        <v>72.816</v>
+        <v>72.817</v>
       </c>
       <c r="R107" s="34">
-        <v>83.726</v>
+        <v>83.727</v>
       </c>
       <c r="S107" s="34">
         <v>94.537</v>
       </c>
       <c r="T107" s="34">
-        <v>98.81</v>
+        <v>98.811</v>
       </c>
       <c r="U107" s="34">
         <v>100</v>
@@ -4816,28 +4816,28 @@
       <c r="K110" s="33"/>
       <c r="L110" s="37"/>
       <c r="M110" s="34">
-        <v>-2.312</v>
+        <v>-2.313</v>
       </c>
       <c r="N110" s="34">
-        <v>-8.943</v>
+        <v>-8.944</v>
       </c>
       <c r="O110" s="34">
         <v>-25.422</v>
       </c>
       <c r="P110" s="34">
-        <v>-55.025</v>
+        <v>-55.026</v>
       </c>
       <c r="Q110" s="34">
-        <v>-72.816</v>
+        <v>-72.817</v>
       </c>
       <c r="R110" s="34">
-        <v>-83.726</v>
+        <v>-83.727</v>
       </c>
       <c r="S110" s="34">
         <v>-94.537</v>
       </c>
       <c r="T110" s="34">
-        <v>-98.81</v>
+        <v>-98.811</v>
       </c>
       <c r="U110" s="34">
         <v>-100</v>
@@ -5088,7 +5088,7 @@
         <v>146</v>
       </c>
       <c r="B2" s="46">
-        <v>2.312</v>
+        <v>2.313</v>
       </c>
       <c r="C2" s="46">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>147</v>
       </c>
       <c r="B3" s="46">
-        <v>8.943</v>
+        <v>8.944</v>
       </c>
       <c r="C3" s="46">
         <v>0</v>
@@ -5130,7 +5130,7 @@
         <v>149</v>
       </c>
       <c r="B5" s="46">
-        <v>55.025</v>
+        <v>55.026</v>
       </c>
       <c r="C5" s="46">
         <v>0</v>
@@ -5144,7 +5144,7 @@
         <v>150</v>
       </c>
       <c r="B6" s="46">
-        <v>72.816</v>
+        <v>72.817</v>
       </c>
       <c r="C6" s="46">
         <v>0</v>
@@ -5155,7 +5155,7 @@
         <v>151</v>
       </c>
       <c r="B7" s="46">
-        <v>83.726</v>
+        <v>83.727</v>
       </c>
       <c r="C7" s="46">
         <v>0</v>
@@ -5177,7 +5177,7 @@
         <v>153</v>
       </c>
       <c r="B9" s="46">
-        <v>98.81</v>
+        <v>98.811</v>
       </c>
       <c r="C9" s="46">
         <v>0</v>
